--- a/src/Tyres.xlsx
+++ b/src/Tyres.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -433,408 +433,149 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BEL-262</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>205/55R16</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>сер легк б/к</t>
-        </is>
-      </c>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BEL-317</t>
+          <t>ФБел-283</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>205/55R16</t>
+          <t>35/65-33</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>сер легк б/к</t>
+          <t>42 груз сер</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BEL-317S</t>
+          <t>BEL-314</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>205/55R16</t>
+          <t>20.5R25</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>сер ошип</t>
+          <t>177 186A2 LS-2 сер Type</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BEL-1001</t>
+          <t>BEL-314</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>235/75R15</t>
+          <t>20.5R25</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>сер легк</t>
+          <t>LS-2 груз сер Type</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BEL-1002</t>
+          <t>BEL-314</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>155/65R13</t>
+          <t>20.5R25</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>сер легк</t>
+          <t>177 186A2 H сер Type</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BEL-1004</t>
+          <t>BEL-314</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>205/55R16</t>
+          <t>20.5R25</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>сер легк</t>
+          <t>H груз сер Type</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BEL-1005</t>
+          <t>BEL-314</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>225/50R17</t>
+          <t>20.5R25</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>сер легк</t>
+          <t>177 186A2 сер C Type</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Бел-202</t>
+          <t>BEL-314</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>24.00R35</t>
+          <t>20.5R25</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>сер Type H 210B</t>
+          <t>груз сер C Type</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BEL-248</t>
+          <t>Бел-230М</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>14.00R20</t>
+          <t>355/65-15</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>сер груз б/к</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Бел-103</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>175/70R13</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>сер легк б/к</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Бел-100</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>175/70R13</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>сер легк б/к</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Ф-35-1</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>11.2-20</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>сер сх 8</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Бел-119</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>195/65R15</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>сер легк</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Бел-1149</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>195/65R15</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>сер легк</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Бел-777</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>210/80R16</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>сер легк</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Бел-1000</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>215/65R16C</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>сер легк</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Бел-1001</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>205/55R16</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>сер легк</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Бел-1005</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>225/50R17</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>сер легк</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>BEL-734</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>205/70R14</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>сер легк б/к</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>BEL-261</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>195/65R15</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>сер легк б/к</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>BEL-337</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>195/65R15</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>сер легк б/к</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>BEL-337S</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>195/65R15</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>сер ошип</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>BEL-705</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>195/65R15</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>сер легк б/к</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Бел-188</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>175/70R13</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>сер легк</t>
+          <t>сер</t>
         </is>
       </c>
     </row>

--- a/src/Tyres.xlsx
+++ b/src/Tyres.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C513"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,117 +463,8664 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BEL-314</t>
+          <t>ФБел-283</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>20.5R25</t>
+          <t>35/65-33</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>177 186A2 LS-2 сер Type</t>
+          <t>30 груз сер</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BEL-314</t>
+          <t>Бел-87</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>20.5R25</t>
+          <t>20.0/60-22.5</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>LS-2 груз сер Type</t>
+          <t>12 груз сер</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BEL-314</t>
+          <t>ФБел-199</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>20.5R25</t>
+          <t>26.5-25</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>177 186A2 H сер Type</t>
+          <t>28 груз сер</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BEL-314</t>
+          <t>ФБел-199</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>20.5R25</t>
+          <t>26.5-25</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>H груз сер Type</t>
+          <t>28 сер б/к</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BEL-314</t>
+          <t>ФБел-199</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>20.5R25</t>
+          <t>26.5-25</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>177 186A2 сер C Type</t>
+          <t>32 груз сер</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BEL-314</t>
+          <t>ФБел-199</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>20.5R25</t>
+          <t>26.5-25</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>груз сер C Type</t>
+          <t>32 сер б/к</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>Бел-6</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>26.5-25</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>28 груз сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Бел-6</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>26.5-25</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>28 груз сер б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Бел-6</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>26.5-25</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>32 груз сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Бел-6</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>26.5-25</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>32 груз сер б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Бел-10М</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>26.5-25</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>28 груз сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Бел-10М</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>26.5-25</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>28 груз сер б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Бел-10М</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>26.5-25</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>32 груз сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Бел-10М</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>26.5-25</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>32 груз сер б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>BEL-315</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>26.5R25</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>груз LS-2 сер Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>BEL-315</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>26.5R25</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>груз сер H Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>BEL-315</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>26.5R25</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>груз C сер Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>BEL-324</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>26.5R25</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>груз LS-2 сер Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>BEL-324</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>26.5R25</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>груз сер H Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>BEL-324</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>26.5R25</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>груз C сер Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>BEL-364</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>26.5R25</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>193B груз LS-2 сер Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>BEL-364</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>26.5R25</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>193B груз сер H Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>BEL-364</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>26.5R25</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>193B груз C сер Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ФБел-150</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>24.00-35</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>42 груз сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Бел-172</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>24.00-35</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>205B груз сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>ФБел-247-1</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>23.5-25</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>20 сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>ФБел-247-1</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>23.5-25</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>20 груз сер б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>ФБел-247-1</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>23.5-25</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>24 сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>ФБел-247-1</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>23.5-25</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>24 сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>ФБел-247-1</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>23.5-25</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>24 груз сер б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Бел-155</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>23.5-25</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>28 груз сер б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Бел-239</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>23.5-25</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>20 груз сер б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Бел-51А</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>21.00-35</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>36 груз сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Бел-51М</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>21.00-35</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>36 груз сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>ВФ-166АМ</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>21.00-33</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>32 груз сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>ИЯВ-79</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>21.3-24</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>12 груз сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>ИЯВ-79</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>21.3-24</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>16 груз сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Ф-92А</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>20.5-25</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>16 груз сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Ф-92А</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>20.5-25</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>16 груз сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Ф-92А</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>20.5-25</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>16 сер б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Ф-92А</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>20.5-25</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>28 груз сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Ф-92А</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>20.5-25</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>28 сер б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Ф-92А</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>20.5-25</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>28 груз сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Ф-92А</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>20.5-25</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>20 груз сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Бел-236</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>20.5-25</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>170B груз сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>BEL-314</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>20.5R25</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>177 186A2 LS-2 сер Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>BEL-314</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>20.5R25</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>груз LS-2 сер Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>BEL-314</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>20.5R25</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>177 186A2 сер H Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>BEL-314</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>20.5R25</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>груз сер H Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>BEL-314</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>20.5R25</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>177 186A2 C сер Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>BEL-314</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>20.5R25</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>груз C сер Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>ВФ-76БМ</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>18.00-25</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>32 груз сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>ВФ-76БМ</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>18.00-25</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>32 груз сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>ВФ-76БМ</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>18.00-25</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>40 груз сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>ВФ-76БМ</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>18.00-25</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>32 груз сер б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>ВФ-76БМ</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>18.00-25</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>36 груз сер б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Бел-12</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>18.00-25</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>28 сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Бел-12</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>18.00-25</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>28 сер б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Бел-12</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>18.00-25</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>28 сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Бел-197</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>18.00-25</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>32 груз сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>BEL-183</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>18.00R25</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>185B груз сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>BEL-183</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>18.00R25</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>185B LS-2 б/к Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>BEL-183</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>18.00R25</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>груз LS-2 сер Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>BEL-183</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>18.00R25</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>185B H б/к Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>BEL-183</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>18.00R25</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>груз сер H Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>BEL-183</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>18.00R25</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>185B C б/к Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>BEL-183</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>18.00R25</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>груз C сер Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>BEL-332</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>18.00-25</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>215A2 груз сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>BEL-425</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>14.00R25</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>170B LS-2 сер L-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>BEL-425</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>14.00R25</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>170B сер H L-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>BEL-425</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>14.00R25</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>170B C сер L-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Бел-71</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>14.5/75-20</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>164A2 груз сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Ф-170</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>17.5-25</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>20 груз сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Ф-170</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>17.5-25</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>22 груз сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Ф-120</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>17.5-25</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>12 груз сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Ф-120</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>17.5-25</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>12 груз сер б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Ф-120</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>17.5-25</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>16 груз сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Ф-120</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>17.5-25</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>16 груз сер б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Ф-120</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>17.5-25</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>20 груз сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Ф-120</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>17.5-25</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>20 сер б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>BEL-301</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>17.5R25</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>182A2 груз сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>BEL-301</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>17.5R25</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>182A2 груз LS-2 сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>BEL-301</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>17.5R25</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>182A2 груз сер H</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>BEL-301</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>17.5R25</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>182A2 груз C сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>BEL-301</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>17.5R25</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>182A2 груз LS-2 сер б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>BEL-301</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>17.5R25</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>182A2 груз сер H б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>BEL-301</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>17.5R25</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>182A2 груз C сер б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>BEL-373</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>17.5R25</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>груз сер б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>BEL-373</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>17.5R25</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>182A2 груз LS-2 сер б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>BEL-373</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>17.5R25</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>182A2 груз сер H б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>BEL-373</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>17.5R25</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>182A2 груз C сер б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>BEL-373</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>17.5R25</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>182A2 груз сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>BEL-373</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>17.5R25</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>182A2 груз LS-2 сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>BEL-373</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>17.5R25</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>182A2 груз сер H</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>BEL-373</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>17.5R25</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>182A2 груз C сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Я-307</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>14.00-20</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>16 груз сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Я-307</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>14.00-20</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>18 груз сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Я-307</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>14.00-20</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>20 груз сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Я-307</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>14.00-20</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>10 груз сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Ф-10А</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>14.00-20</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>20 груз сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Бел-67А</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>14.00-20</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>22 груз сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Бел-64</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>14.00-20</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>10 груз сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Бел-64</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>14.00-20</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>14 груз сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Бел-64</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>14.00-20</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>14 груз сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Бел-64</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>14.00-20</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>22 груз сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>BEL-20</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>14.00-20</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>188A2 груз сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Бел-26.42.38</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>29.5/75R25</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>26 груз сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Бел-32.48.75</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>29.5/75R25</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>26 сер б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Бел-32.48.75</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>29.5/75R25</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>26 сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>ВИ-3</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>1300x530-533</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>12 груз сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Бел-66А</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>525/70R21</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>16 груз сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Бел-66А</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>525/70R21</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>172D груз сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>ВИ-203</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>1500x600-635</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>14 груз сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>ВИ-203</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>1500x600-635</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>176E груз сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>BEL-304</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>29.5R25</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>груз LS-2 сер Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>BEL-304</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>29.5R25</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>груз сер H Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>BEL-304</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>29.5R25</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>груз C сер Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>BEL-325</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>29.5R25</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>200B груз LS-2 сер Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>BEL-325</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>29.5R25</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>200B груз сер H Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>BEL-325</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>29.5R25</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>200B груз C сер Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>BEL-365</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>29.5R25</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>200B груз LS-2 сер Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>BEL-365</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>29.5R25</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>200B груз сер H Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>BEL-365</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>29.5R25</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>200B груз C сер Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>BEL-323</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>23.5R25</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>185B LS-2 б/к Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>BEL-323</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>23.5R25</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>185B груз LS-2 сер Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>BEL-323</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>23.5R25</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>185B H б/к Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>BEL-323</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>23.5R25</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>185B груз сер H Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>BEL-323</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>23.5R25</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>185B C б/к Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>BEL-323</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>23.5R25</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>185B груз C сер Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>BEL-375</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>23.5R25</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>185B груз LS-2 сер Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>BEL-375</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>23.5R25</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>185B груз сер H Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>BEL-375</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>23.5R25</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>185B груз C сер Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>BEL-305</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>29.5R29</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>груз LS-2 сер Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>BEL-305</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>29.5R29</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>груз сер H Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>BEL-305</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>29.5R29</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>груз C сер Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>BEL-379</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>29.5R29</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>груз LS-2 сер Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>BEL-379</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>29.5R29</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>груз сер H Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>BEL-379</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>29.5R29</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>груз C сер Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Бел-83М</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>28LR26</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>168B груз сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Бел-1260</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>425/85R21</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Бел-1260</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>425/85R21</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>ФД-12</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>28.1R26</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>158A8 сер сх</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>ФД-12</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>28.1R26</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>170A6 сер сх</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Бел-83М</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>28LR26</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>165A8 сер сх</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Бел-83М</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>28LR26</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>165A8 сер сх б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Ф-179</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>30.5L-32</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>12 сер сх</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Ф-179</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>30.5L-32</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>170A6 сх</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Ф-81</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>30.5R32</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>12 сер сх</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Ф-81</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>30.5R32</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>172A8 сер сх</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>ФБел-179М</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>30.5L-32</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>12 сер сх</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>ФБел-179М</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>30.5L-32</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>18 сер сх</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>ФБел-179М</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>30.5L-32</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>169A8 сер сх</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Ф-118А</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>22.0/70-20</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>10 сер сх</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Бел-91</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>24.0/50-22.5</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>12 сер б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Бел-91</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>24.0/50-22.5</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>12 сер сх</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Бел-91</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>24.0/50-22.5</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>16 сер б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Бел-91</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>24.0/50-22.5</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>16 сер сх</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Бел-91</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>24.0/50-22.5</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>12 сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>BEL-33</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>600/50-22.5</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>156A8 сер сх</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>BEL-34</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>560/60-22.5</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>167A8 сер сх</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>BEL-41</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>600/55-26.5</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>166A8 сер сх</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>BEL-42</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>600/55-26.5</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>166A8 сер сх</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>ИЯВ-79</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>21.3-24</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>10 сер сх</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>ИЯВ-79</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>21.3-24</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>12 сер сх</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Бел-126М</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>580/70R42</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>158D сер сх</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Бел-126М</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>580/70R42</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>158D сер б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>BEL-35</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>400/55-22.5</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>147A8 сер сх</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>BEL-36</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>500/60-22.5</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>155A8 сер сх</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>BEL-37</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>500/60-22.5</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>155A8 сер сх</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Бел-15</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>20.8R38</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>153A8 сер сх</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Бел-15</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>20.8R38</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>161A8 сер сх</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>BEL-49</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>480/80R42(18.4R42</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>151A8 сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Ф-111</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>18.4R38</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>146A8 сер сх</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Бел-87</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>20.0/60-22.5</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>12 сер сх</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Бел-87</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>20.0/60-22.5</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>12 сер б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Бел-87</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>20.0/60-22.5</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>16 163A6 сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Ф-44</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>18.4R34</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>141A6 сер сх</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Ф-11</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>18.4R34</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>144A8 сер сх</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Ф-11</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>18.4R34</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>144A8 сер сх</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Бел-27</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>18.4R30</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>12 сер сх</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Бел-129</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>480/70R30</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>сер сх</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Бел-129</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>480/70R30</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>141A8 сер сх б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>BEL-38</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>560/45-22.5</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>154A8 сер сх</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Бел-136</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>480/65R24</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>133A8 сер сх</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Ф-148</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>18.4-24</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>28 сер сх</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Ф-148</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>18.4-24</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>10 сер сх</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Бел-93</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>620/75R26</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>166A8 сер сх</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Бел-93</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>620/75R26</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>сер сх б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Бел-93</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>620/75R26</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>148A8 сер сх</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Бел-93</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>620/75R26</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>166A8 сер сх</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Бел-90</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>420/70R24</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>130A8 сер сх</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Бел-90</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>420/70R24</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>130A8 сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Бел-89</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>360/70R24</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>сер сх</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Бел-89</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>360/70R24</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>122A8 сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>BEL-45</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>520/50-17</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>159A8 сер сх</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Ф-52</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>16.9R38</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>28 сер сх</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Бел-111</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>520/70R38</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>сер сх</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Бел-111</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>520/70R38</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>150A8 сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>BEL-43</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>710/45-26.5</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>163A8 сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Ф-39</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>16.9R30</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>28 сер сх</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Ф-245-1</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>16.9R30</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>28 сер сх</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Бел-186</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>11.2R24</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>114A8 сер б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Бел-186</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>11.2R24</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>114A8 сер сх</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Бел-206</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8.25-15 </t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>28 сер сх</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>BEL-251</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>520/70R34</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>148A8 сер б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>BEL-251</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>520/70R34</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>148A8 сер сх</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>BEL-39</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>620/50B22.5</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>160D сер сх</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>BEL-40</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>500/45-22.5</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>146A8 сер сх</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>КФ-97</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>16.5/70-18</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>10 сер сх</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>КФ-97</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>16.5/70-18</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>14 сер сх</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>КФ-97М</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>16.5/70-18</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>149A6 сер сх</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>КФ-97М</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>16.5/70-18</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>153A6 сер сх</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Бел-79</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>16.5-18</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>L-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Бел-79</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>16.5-18</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>42 сер сх</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Ф-76-1</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>16.0-20</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>28 сер сх</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>Ф-64GL-1</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>16.0-20</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>12 сер сх</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Ф-64GL-1</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>16.0-20</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>28 сер сх</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Ф-64GL-1</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>16.0-20</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>14 сер сх</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Бел-139</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>16x6.50-8</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>сер сх</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>BEL-57</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>600/70R30</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>159D сер сх</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Ф-2А</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>15.5R38</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>28 сер сх</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>BEL-55</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>13.6R38</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>сер сх</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Бел-163</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>14.9R30</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>129A8 сер сх</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Бел-17</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>13.6-20</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>28 сер сх</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>ФБел-340</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>13.0/75-16</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>28 сер сх</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>ФБел-340</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>13.0/75-16</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>10 сер сх</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>ФБел-340</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>13.0/75-16</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>14 сер сх</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Бел-104</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>13.0/75-16</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>28 сер сх</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Бел-104</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>13.0/75-16</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>10 сер сх</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>ФБел-160М</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>12,4L-16</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>сер сх</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>Ф-35-1</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>11.2-20</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>28 сер сх</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>Ф-35-1</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>11.2-20</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>124A8 сер сх</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>Бел-92</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>10.0/75-15.3</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>28 сер сх</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>Бел-92</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>10.0/75-15.3</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>10 сер сх</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>Бел ПТ-5М</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>10.00-16</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>сер сх</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>ПТ-5М</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>10.00-16</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>сер сх</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>ПТ-5М</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>10.00-16</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>Бел ПТ-5М</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9.00-16 </t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>10 сер сх</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>Бел ПТ-5М</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9.00-16 </t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>10 сер сх</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>Бел-226</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9.00-16 </t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>104A6 вен.161 сер сх</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>Бел-226</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9.00-16 </t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>104A6 вен.161 сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>В-103</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7.50-20 </t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>сер сх</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>ФБел-253М</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7.50L-16 </t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>сер сх L-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>ФБел-253М</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7.50L-16 </t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>42 сер сх</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>Ф-140М</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>6L-12</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>сер сх L-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>Я-275А</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6.50-16 </t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>вен.161 сер сх</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>ФБел-256</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.50-16 </t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>42 сер сх</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>ФБел-256</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.50-16 </t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>28 сер сх</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>ФБел-256М</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.50-16 </t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>12 сер сх</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>Ф-122</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.50-16 </t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>28 сер сх</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>Ф-122</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.50-16 </t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>42 сер сх</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>В-19А</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.00-10 </t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>вен.161 сер сх</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>В-19А</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.00-10 </t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>10 сер сх</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>Бел-68</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>14.9R24</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>126A8 сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>BEL-68</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>14.9R24</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>126A8 сер сх</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>Бел-141</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>800/65R32</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>167A8 сер б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>BEL-141</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>800/65R32</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>167A8 сер сх</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>BEL-141</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>800/65R32</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>178A8 сер сх</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>BEL-141</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>800/65R32</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>178A8 сер б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>BEL-47</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>900/60R32</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>188A8 сер сх</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>BEL-48</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>050/50R32</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>180A8 сер сх</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>Бел-165</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>600/65R34</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>151D сер сх</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>BEL-165</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>600/65R34</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>151D сер сх</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>BEL-176</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>600/65R28</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>147A8 сх</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>BEL-176</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>600/65R28</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>154A8 сер сх</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>BEL-176</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>600/65R28</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>162A8 сер сх</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>BEL-244</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>650/65R42</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>168A8 сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>BEL-244</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>650/65R42</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>168A8 сер б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>Бел-245</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>700/50-22.5</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>174A8 сер сх</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>Бел-194</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>700/50-26.0</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>16 сер сх</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>Бел-194</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>700/50-26.0</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>20 сер сх</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>Бел-194</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>700/50-26.0</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>24 сер сх</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>Бел-179</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>710/70R38</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>166D сер сх</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>Бел-175</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>710/70R42</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>173D сер сх</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>Бел-225</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9.50-20 </t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>101A6 сер сх</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>Бел-144</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>540/65R30</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>150A8 сер сх</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>Бел-144</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>540/65R30</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>150A8 сер б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>Бел-173</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>12,5/80-15,3</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>Бел-104</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>12,0-16</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>28 сер сх</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>Ф-65-1</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>18x7-8</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>10 сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>Ф-64 GL-1</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>16.0-20</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>14 сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>Бел-1</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8.15-15 </t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>14 сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>BEL-53</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 12-16.5</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>145A2 сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>BEL-52</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 10-16.5</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>135A2 сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>Ф-42-1</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7.00-12 </t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>12 сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>Бел-135</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6.50-10 </t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>14 сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>В-98-1</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6.00-13 </t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>10 сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>В-98-1</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6.00-13 </t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>12 сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>В-97-1</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6.25-10 </t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>10 сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>В-97-1</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6.25-10 </t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>Бел-11</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>215/90-15C</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>вен.161 сер легк</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>БелОШ2</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>24.0/50-22.5</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>BEL-158M</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>315/80R22.5</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>груз камневыт сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>BEL-278</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>315/80R22.5</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>груз сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>BEL-268</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>315/80R22.5</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>груз сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>BEL-398</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>315/80R22.5</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>груз сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>BEL-326</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>315/80R22.5</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>груз сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>BEL-498</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>315/80R22.5</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>156L груз сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>ИД-304М</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>12.00R20</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>16 груз сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>ИД-304М</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>12.00R20</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>18 груз сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>БИ-368М</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>12.00R20</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>18 груз сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>Бел-116</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>12.00R20</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>18 груз сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>BEL-306</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>12.00R20</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>груз сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>И-111АМ</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>11.00R20</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>груз сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>Бел-124</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>11.00R20</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>груз сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>Бел-310</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>11.00R20</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>груз сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>BEL-311</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>11.00R20</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>груз сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>Бел-114</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>10.00R20</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>16 груз сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>Бел-114</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>10.00R20</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>18 груз сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>Бел-114</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>10.00R20</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>18 груз сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>Бел-310</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>10.00R20</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>16 груз сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>BEL-312</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>10.00R20</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>груз сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>BEL-312</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>10.00R20</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>груз сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>BEL-368</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 13R22.5</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>груз сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>БИ-366</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9.00R20 </t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>14 груз сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>И-Н142Б</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9.00R20 </t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>12 груз сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>И-Н142Б</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9.00R20 </t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>14 груз сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>К-84МБ</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8.25R20 </t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>10 груз сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>К-84МБ</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8.25R20 </t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>12 груз сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>Бел-146</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>385/65R22.5</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>груз сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>BEL-298</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 11R22.5</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>груз сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>BEL-296</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 11R22.5</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>груз сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>BEL-238</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>12.00R24</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>груз сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>BEL-308</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>12.00R24</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>груз сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>Бел-108М</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>275/70R22.5</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>груз сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>BEL-318</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>275/70R22.5</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>груз сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>Бел-168</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>245/70R19.5</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>груз сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>Бел-178</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>295/80R22.5</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>16 груз сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>BEL-246</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>295/80R22.5</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>груз камневыт сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>BEL-266</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>295/80R22.5</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>152K груз сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>BEL-418</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>295/80R22.5</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>груз сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>BEL-328</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>295/80R22.5</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>груз сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>BEL-195</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>265/70R19.5</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>груз сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>BEL-198</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>385/55R22.5</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>груз сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>Бел-159</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>235/75R17.5</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>груз сер б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>BEL-196</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>235/75R17.5</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>груз сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>BEL-208</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>235/75R17.5</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>груз сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>BEL-138М</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>315/70R22.5</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>груз сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>BEL-148М</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>315/70R22.5</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>груз сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>BEL-488</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>315/70R22.5</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>груз сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>Бел-169</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>215/75R17.5</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>груз сер б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>BEL-258</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 12R22.5</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>груз сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>BEL-358</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 12R22.5</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>груз сер б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>BEL-376</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>315/60R22.5</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>груз сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>BEL-356</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>315/60R22.5</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>груз сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>ФБел-311</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9.00R20 </t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>вен.161 сер сх</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>Бел-161</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>265/70R16</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>102A8 сер сх</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>Бел-219</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>210/75R13</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>сер сх</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>Бел-166</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>210/80R16</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>сер сх</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>Бел-166</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>210/80R16</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>сер сх</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>Бел-31</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9.00R20 </t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>сер сх</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>Бел-121</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>205/70R15</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>сер легк б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>BEL-715</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>205/70R15</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>сер легк б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>Бел-59</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>205/70R14</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>сер легк б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>BEL-734</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>205/70R14</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>сер легк б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>Бел-119</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>195/65R15</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>сер легк</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>BEL-261</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>195/65R15</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>сер легк б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>BEL-337</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>195/65R15</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>сер легк б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>BEL-337S</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>195/65R15</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>сер ошип</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>BEL-705</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>195/65R15</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>сер легк б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>Бел-107М</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>185/65R14</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>сер ошип</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>Бел-157</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>185/65R14</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>сер легк б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>BEL-254</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>185/65R14</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>сер легк б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>BEL-147</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>185/65R14</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>сер легк б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>BEL-147S</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>185/65R14</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>сер ошип</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>BEL-704</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>185/65R14</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>сер легк б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>BEL-297</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>205/65R15</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>сер легк б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>BEL-279</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>205/65R15</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>сер легк б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>BEL-725</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>205/65R15</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>сер легк б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>Бел-103</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>175/70R13</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>сер легк б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>Бел-100</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>175/70R13</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>сер легк б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>Бел-188</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>175/70R13</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>сер легк</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>Бел-188М</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>175/70R13</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>сер б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>BEL-253</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>175/70R13</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>сер легк б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>BEL-253</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>175/70R13</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>сер легк</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>BEL-347</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>175/70R13</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>сер легк б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>Бел-127М</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>175/70R13</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>сер ошип</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>BEL-264</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>175/65R14</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>сер легк б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>BEL-264</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>175/65R14</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>сер легк</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>BEL-357</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>175/65R14</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>сер легк б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>BEL-227S</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>175/65R14</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>сер ошип</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>Бел-177</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>185/65R15</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>сер легк б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>BEL-287</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>185/65R15</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>сер легк б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>BEL-280</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>185/65R15</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>сер легк б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>BEL-280</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>185/65R15</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>сер легк</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>BEL-367</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>185/60R15</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>сер легк б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>BEL-327</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>185/60R15</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>сер легк б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>BEL-327S</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>185/60R15</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>сер ошип</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>BEL-286</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>185/60R15</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>сер легк б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>BEL-294</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>195/55R16</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>сер легк б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>BEL-457</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>195/55R16</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>сер легк б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>BEL-256</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>185/60R14</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>сер легк б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>BEL-256</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>185/60R14</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>сер легк</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>BEL-267</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>185/60R14</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>сер легк б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>BEL-714</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>185/60R14</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>сер легк б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>Бел-97</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>185/70R14</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>сер легк б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>Бел-117</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>185/70R14</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>сер легк б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>Бел-117М</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>185/70R14</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>сер ошип</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>BEL-274</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>185/70R14</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>сер легк б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>BEL-397</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>185/70R14</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>сер легк б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>BEL-397S</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>185/70R14</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>сер ошип</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>BEL-724</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>185/70R14</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>сер легк б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>BEL-262</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>205/55R16</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>сер легк б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>BEL-317</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>205/55R16</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>сер легк б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>BEL-317S</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>205/55R16</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>сер ошип</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>BEL-277</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>205/60R16</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>сер легк б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>BEL-282</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>205/60R16</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>сер легк б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>BEL-284</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>205/55R15</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>сер легк б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>BEL-447</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>205/55R15</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>сер легк б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>BEL-341</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>205/75R15</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>сер легк б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>BEL-345</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>205/70R16</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>сер легк б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>BEL-329</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>215/55R16</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>сер легк б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>BEL-716</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>215/55R16</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>сер легк б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>BEL-679</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>215/55R16</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>сер легк б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>BEL-217</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>215/65R16</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>сер легк б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>BEL-330</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>215/65R16</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>сер легк б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>BEL-706</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>215/65R16</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>сер легк б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>Бел-257</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>215/60R16</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>сер легк б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>BEL-283</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>215/60R16</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>сер легк б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>BEL-377</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>215/60R16</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>сер легк б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>BEL-377S</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>215/60R16</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>сер ошип</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>BEL-273</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>235/60R16</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>сер легк б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>BEL-270</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>205/65R16</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>сер легк б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>BEL-467</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>205/65R16</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>сер легк б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>BEL-529</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>235/55R17</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>сер легк б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>BEL-627</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>235/55R17</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>сер легк б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>BEL-579</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>235/55R18</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>сер легк б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>BEL-412</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>215/55R18</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>сер легк б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>BEL-429</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>245/45R18</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>сер легк б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>BEL-307</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>195/60R15</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>сер легк б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>BEL-307S</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>195/60R15</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>сер ошип</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>BEL-281</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>195/60R15</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>сер легк б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>BEL-402</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>215/60R17</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>сер легк б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>BEL-464</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>215/60R17</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>сер легк б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>BEL-409</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>215/55R17</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>сер легк б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>BEL-344</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>215/70R16</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>сер легк б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>BEL-539</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>225/50R17</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>сер легк б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>BEL-403</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>225/60R18</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>сер легк б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>BEL-494</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>225/60R18</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>сер легк б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>BEL-331</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>225/55R16</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>сер легк б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>BEL-334</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>225/60R16</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>сер легк б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>BEL-487</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>225/60R16</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>сер легк б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>BEL-354</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>225/60R17</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>сер легк б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>BEL-441</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>225/55R18</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>сер легк</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>BEL-275</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>225/75R16</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>сер легк б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>BEL-285</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>225/45R17</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>сер легк б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>BEL-295</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>225/65R17</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>сер легк б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>BEL-517</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>225/65R17</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>сер легк б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>BEL-509</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>225/65R17</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>сер легк б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>BEL-411</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>225/65R17</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>сер легк б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>BEL-719</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>225/65R17</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>сер легк б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>BEL-491</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>255/55R18</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>сер легк б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>BEL-451</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>235/60R18</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>сер легк б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>Бел-171</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>195/70R15C</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>сер л/г б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>BEL-333</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>195/70R15C</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>сер л/г б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>BEL-303</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>195/75R16C</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>сер л/г б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>Бел-77</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>225/70R15C</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>сер л/г б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>BEL-353</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>225/70R15C</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>BEL-313</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>215/75R16C</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>Бел-143</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>205/70R15C</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>BEL-300</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>235/65R16C</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>Бел-78</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>195R14C</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>сер л/г б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>BEL-343</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>195R14C</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>Бел-109</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>185/75R16C</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>Бел-109</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>185/75R16C</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>сер б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>BEL-293</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>185/75R16C</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>BEL-293S</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>185/75R16C</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>сер ошип</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>BEL-293</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>185/75R16C</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>сер б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>BEL-293S</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>185/75R16C</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>сер л/г б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>БИ-522</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>175R16C</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>сер л/г</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>БИ-522</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>175R16C</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>сер л/г</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>БИ-522</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>175R16C</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>сер легк б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>ФТ-117М</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>40.00-57</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>68 груз сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>Бел-160Д</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>46/90-57</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>68 груз сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>ФТ-116АМ2</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>33.00-51</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>58 груз сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>Бел-180</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>36/90-51</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>58 груз сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>Бел-182</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>31/90-49</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>54 груз сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>ФТ-115</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>27.00-49</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>48 груз сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>Бел-174</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>24.00-49</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>48 груз сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>Бел-122</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>24.00R35</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>груз LS-2 сер Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>Бел-122</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>24.00R35</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>груз сер H Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>Бел-122</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>24.00R35</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>груз C сер Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>Бел-202</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>24.00R35</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>210B LS-2 сер Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>Бел-202</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>24.00R35</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>210B сер H Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>Бел-202</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>24.00R35</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>210B C сер Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>Бел-212</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>24.00R35</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>груз LS-2 сер Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>Бел-212</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>24.00R35</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>груз сер H Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>Бел-212</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>24.00R35</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>груз C сер Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>Бел-200</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>21.00R35</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>202B LS-2 сер Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>Бел-200</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>21.00R35</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>202B сер H Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>Бел-200</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>21.00R35</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>202B C сер Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>Бел-210</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>21.00R35</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>202B LS-2 сер Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>Бел-210</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>21.00R35</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>202B сер H Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>Бел-210</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>21.00R35</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>202B C сер Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>BEL-248</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>14.00R20</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>груз сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>BEL-248</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>14.00R20</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>груз сер б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>BEL-248</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>14.00R20</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>груз сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>BEL-248</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>14.00R20</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>груз сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>BEL-288</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>12.00R20</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>груз сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>Бел-95</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>16.00R20</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>173G груз сер б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>Бел-95</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>16.00R20</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>173G груз сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>Бел-95</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>16.00R20</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>173G груз сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>Бел-95</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>16.00R20</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>173G груз сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>Бел-95</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>16.00R20</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>173G груз сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>Бел-95</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>16.00R20</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>173G груз сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>Бел-95</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>16.00R20</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>173G сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>BEL-405</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>395/85R20</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>168J груз сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>Бел-145</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>445/65R22.5</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>груз сер б/к</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>Бел-230</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>355/65-15</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>сер</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
           <t>Бел-230М</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B513" t="inlineStr">
         <is>
           <t>355/65-15</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C513" t="inlineStr">
         <is>
           <t>сер</t>
         </is>

--- a/src/Tyres.xlsx
+++ b/src/Tyres.xlsx
@@ -456,7 +456,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>42 груз сер</t>
+          <t>42 сер груз</t>
         </is>
       </c>
     </row>
@@ -473,7 +473,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>30 груз сер</t>
+          <t>30 сер груз</t>
         </is>
       </c>
     </row>
@@ -490,7 +490,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>12 груз сер</t>
+          <t>12 сер груз</t>
         </is>
       </c>
     </row>
@@ -507,7 +507,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>28 груз сер</t>
+          <t>28 сер груз</t>
         </is>
       </c>
     </row>
@@ -541,7 +541,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>32 груз сер</t>
+          <t>32 сер груз</t>
         </is>
       </c>
     </row>
@@ -575,7 +575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>28 груз сер</t>
+          <t>28 сер груз</t>
         </is>
       </c>
     </row>
@@ -592,7 +592,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>28 груз сер б/к</t>
+          <t>28 сер б/к груз</t>
         </is>
       </c>
     </row>
@@ -609,7 +609,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>32 груз сер</t>
+          <t>32 сер груз</t>
         </is>
       </c>
     </row>
@@ -626,7 +626,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>32 груз сер б/к</t>
+          <t>32 сер б/к груз</t>
         </is>
       </c>
     </row>
@@ -643,7 +643,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>28 груз сер</t>
+          <t>28 сер груз</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>28 груз сер б/к</t>
+          <t>28 сер б/к груз</t>
         </is>
       </c>
     </row>
@@ -677,7 +677,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>32 груз сер</t>
+          <t>32 сер груз</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>32 груз сер б/к</t>
+          <t>32 сер б/к груз</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>груз LS-2 сер Type</t>
+          <t>Type LS-2 сер груз</t>
         </is>
       </c>
     </row>
@@ -728,7 +728,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>груз сер H Type</t>
+          <t>Type сер H груз</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>груз C сер Type</t>
+          <t>Type сер C груз</t>
         </is>
       </c>
     </row>
@@ -762,7 +762,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>груз LS-2 сер Type</t>
+          <t>Type LS-2 сер груз</t>
         </is>
       </c>
     </row>
@@ -779,7 +779,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>груз сер H Type</t>
+          <t>Type сер H груз</t>
         </is>
       </c>
     </row>
@@ -796,7 +796,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>груз C сер Type</t>
+          <t>Type сер C груз</t>
         </is>
       </c>
     </row>
@@ -813,7 +813,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>193B груз LS-2 сер Type</t>
+          <t>193B Type LS-2 сер груз</t>
         </is>
       </c>
     </row>
@@ -830,7 +830,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>193B груз сер H Type</t>
+          <t>193B Type сер H груз</t>
         </is>
       </c>
     </row>
@@ -847,7 +847,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>193B груз C сер Type</t>
+          <t>193B Type сер C груз</t>
         </is>
       </c>
     </row>
@@ -864,7 +864,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>42 груз сер</t>
+          <t>42 сер груз</t>
         </is>
       </c>
     </row>
@@ -881,7 +881,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>205B груз сер</t>
+          <t>205B сер груз</t>
         </is>
       </c>
     </row>
@@ -915,7 +915,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>20 груз сер б/к</t>
+          <t>20 сер б/к груз</t>
         </is>
       </c>
     </row>
@@ -966,7 +966,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>24 груз сер б/к</t>
+          <t>24 сер б/к груз</t>
         </is>
       </c>
     </row>
@@ -983,7 +983,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>28 груз сер б/к</t>
+          <t>28 сер б/к груз</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>20 груз сер б/к</t>
+          <t>20 сер б/к груз</t>
         </is>
       </c>
     </row>
@@ -1017,7 +1017,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>36 груз сер</t>
+          <t>36 сер груз</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>36 груз сер</t>
+          <t>36 сер груз</t>
         </is>
       </c>
     </row>
@@ -1051,7 +1051,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>32 груз сер</t>
+          <t>32 сер груз</t>
         </is>
       </c>
     </row>
@@ -1068,7 +1068,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>12 груз сер</t>
+          <t>12 сер груз</t>
         </is>
       </c>
     </row>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>16 груз сер</t>
+          <t>16 сер груз</t>
         </is>
       </c>
     </row>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>16 груз сер</t>
+          <t>16 сер груз</t>
         </is>
       </c>
     </row>
@@ -1119,7 +1119,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>16 груз сер</t>
+          <t>16 сер груз</t>
         </is>
       </c>
     </row>
@@ -1153,7 +1153,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>28 груз сер</t>
+          <t>28 сер груз</t>
         </is>
       </c>
     </row>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>28 груз сер</t>
+          <t>28 сер груз</t>
         </is>
       </c>
     </row>
@@ -1204,7 +1204,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>20 груз сер</t>
+          <t>20 сер груз</t>
         </is>
       </c>
     </row>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>170B груз сер</t>
+          <t>170B сер груз</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>177 186A2 LS-2 сер Type</t>
+          <t>177 186A2 Type LS-2 сер</t>
         </is>
       </c>
     </row>
@@ -1255,7 +1255,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>груз LS-2 сер Type</t>
+          <t>Type LS-2 сер груз</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>177 186A2 сер H Type</t>
+          <t>177 186A2 Type сер H</t>
         </is>
       </c>
     </row>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>груз сер H Type</t>
+          <t>Type сер H груз</t>
         </is>
       </c>
     </row>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>177 186A2 C сер Type</t>
+          <t>177 186A2 Type сер C</t>
         </is>
       </c>
     </row>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>груз C сер Type</t>
+          <t>Type сер C груз</t>
         </is>
       </c>
     </row>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>32 груз сер</t>
+          <t>32 сер груз</t>
         </is>
       </c>
     </row>
@@ -1357,7 +1357,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>32 груз сер</t>
+          <t>32 сер груз</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>40 груз сер</t>
+          <t>40 сер груз</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>32 груз сер б/к</t>
+          <t>32 сер б/к груз</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>36 груз сер б/к</t>
+          <t>36 сер б/к груз</t>
         </is>
       </c>
     </row>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>32 груз сер</t>
+          <t>32 сер груз</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>185B груз сер</t>
+          <t>185B сер груз</t>
         </is>
       </c>
     </row>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>185B LS-2 б/к Type</t>
+          <t>185B Type LS-2 б/к</t>
         </is>
       </c>
     </row>
@@ -1527,7 +1527,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>груз LS-2 сер Type</t>
+          <t>Type LS-2 сер груз</t>
         </is>
       </c>
     </row>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>185B H б/к Type</t>
+          <t>185B Type H б/к</t>
         </is>
       </c>
     </row>
@@ -1561,7 +1561,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>груз сер H Type</t>
+          <t>Type сер H груз</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>185B C б/к Type</t>
+          <t>185B Type б/к C</t>
         </is>
       </c>
     </row>
@@ -1595,7 +1595,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>груз C сер Type</t>
+          <t>Type сер C груз</t>
         </is>
       </c>
     </row>
@@ -1612,7 +1612,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>215A2 груз сер</t>
+          <t>215A2 сер груз</t>
         </is>
       </c>
     </row>
@@ -1663,7 +1663,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>170B C сер L-2</t>
+          <t>170B сер C L-2</t>
         </is>
       </c>
     </row>
@@ -1680,7 +1680,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>164A2 груз сер</t>
+          <t>164A2 сер груз</t>
         </is>
       </c>
     </row>
@@ -1697,7 +1697,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>20 груз сер</t>
+          <t>20 сер груз</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>22 груз сер</t>
+          <t>22 сер груз</t>
         </is>
       </c>
     </row>
@@ -1731,7 +1731,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>12 груз сер</t>
+          <t>12 сер груз</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>12 груз сер б/к</t>
+          <t>12 сер б/к груз</t>
         </is>
       </c>
     </row>
@@ -1765,7 +1765,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>16 груз сер</t>
+          <t>16 сер груз</t>
         </is>
       </c>
     </row>
@@ -1782,7 +1782,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>16 груз сер б/к</t>
+          <t>16 сер б/к груз</t>
         </is>
       </c>
     </row>
@@ -1799,7 +1799,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>20 груз сер</t>
+          <t>20 сер груз</t>
         </is>
       </c>
     </row>
@@ -1833,7 +1833,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>182A2 груз сер</t>
+          <t>182A2 сер груз</t>
         </is>
       </c>
     </row>
@@ -1850,7 +1850,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>182A2 груз LS-2 сер</t>
+          <t>182A2 LS-2 сер груз</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>182A2 груз сер H</t>
+          <t>182A2 сер H груз</t>
         </is>
       </c>
     </row>
@@ -1884,7 +1884,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>182A2 груз C сер</t>
+          <t>182A2 сер C груз</t>
         </is>
       </c>
     </row>
@@ -1901,7 +1901,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>182A2 груз LS-2 сер б/к</t>
+          <t>182A2 LS-2 сер б/к груз</t>
         </is>
       </c>
     </row>
@@ -1918,7 +1918,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>182A2 груз сер H б/к</t>
+          <t>182A2 сер H б/к груз</t>
         </is>
       </c>
     </row>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>182A2 груз C сер б/к</t>
+          <t>182A2 сер б/к C груз</t>
         </is>
       </c>
     </row>
@@ -1952,7 +1952,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>груз сер б/к</t>
+          <t>сер б/к груз</t>
         </is>
       </c>
     </row>
@@ -1969,7 +1969,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>182A2 груз LS-2 сер б/к</t>
+          <t>182A2 LS-2 сер б/к груз</t>
         </is>
       </c>
     </row>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>182A2 груз сер H б/к</t>
+          <t>182A2 сер H б/к груз</t>
         </is>
       </c>
     </row>
@@ -2003,7 +2003,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>182A2 груз C сер б/к</t>
+          <t>182A2 сер б/к C груз</t>
         </is>
       </c>
     </row>
@@ -2020,7 +2020,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>182A2 груз сер</t>
+          <t>182A2 сер груз</t>
         </is>
       </c>
     </row>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>182A2 груз LS-2 сер</t>
+          <t>182A2 LS-2 сер груз</t>
         </is>
       </c>
     </row>
@@ -2054,7 +2054,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>182A2 груз сер H</t>
+          <t>182A2 сер H груз</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>182A2 груз C сер</t>
+          <t>182A2 сер C груз</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>16 груз сер</t>
+          <t>16 сер груз</t>
         </is>
       </c>
     </row>
@@ -2105,7 +2105,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>18 груз сер</t>
+          <t>18 сер груз</t>
         </is>
       </c>
     </row>
@@ -2122,7 +2122,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>20 груз сер</t>
+          <t>20 сер груз</t>
         </is>
       </c>
     </row>
@@ -2139,7 +2139,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>10 груз сер</t>
+          <t>10 сер груз</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>20 груз сер</t>
+          <t>20 сер груз</t>
         </is>
       </c>
     </row>
@@ -2173,7 +2173,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>22 груз сер</t>
+          <t>22 сер груз</t>
         </is>
       </c>
     </row>
@@ -2190,7 +2190,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>10 груз сер</t>
+          <t>10 сер груз</t>
         </is>
       </c>
     </row>
@@ -2207,7 +2207,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>14 груз сер</t>
+          <t>14 сер груз</t>
         </is>
       </c>
     </row>
@@ -2224,7 +2224,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>14 груз сер</t>
+          <t>14 сер груз</t>
         </is>
       </c>
     </row>
@@ -2241,7 +2241,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>22 груз сер</t>
+          <t>22 сер груз</t>
         </is>
       </c>
     </row>
@@ -2258,7 +2258,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>188A2 груз сер</t>
+          <t>188A2 сер груз</t>
         </is>
       </c>
     </row>
@@ -2275,7 +2275,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>26 груз сер</t>
+          <t>26 сер груз</t>
         </is>
       </c>
     </row>
@@ -2326,7 +2326,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>12 груз сер</t>
+          <t>12 сер груз</t>
         </is>
       </c>
     </row>
@@ -2343,7 +2343,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>16 груз сер</t>
+          <t>16 сер груз</t>
         </is>
       </c>
     </row>
@@ -2360,7 +2360,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>172D груз сер</t>
+          <t>172D сер груз</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2377,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>14 груз сер</t>
+          <t>14 сер груз</t>
         </is>
       </c>
     </row>
@@ -2394,7 +2394,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>176E груз сер</t>
+          <t>176E сер груз</t>
         </is>
       </c>
     </row>
@@ -2411,7 +2411,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>груз LS-2 сер Type</t>
+          <t>Type LS-2 сер груз</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>груз сер H Type</t>
+          <t>Type сер H груз</t>
         </is>
       </c>
     </row>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>груз C сер Type</t>
+          <t>Type сер C груз</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>200B груз LS-2 сер Type</t>
+          <t>200B Type LS-2 сер груз</t>
         </is>
       </c>
     </row>
@@ -2479,7 +2479,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>200B груз сер H Type</t>
+          <t>200B Type сер H груз</t>
         </is>
       </c>
     </row>
@@ -2496,7 +2496,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>200B груз C сер Type</t>
+          <t>200B Type сер C груз</t>
         </is>
       </c>
     </row>
@@ -2513,7 +2513,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>200B груз LS-2 сер Type</t>
+          <t>200B Type LS-2 сер груз</t>
         </is>
       </c>
     </row>
@@ -2530,7 +2530,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>200B груз сер H Type</t>
+          <t>200B Type сер H груз</t>
         </is>
       </c>
     </row>
@@ -2547,7 +2547,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>200B груз C сер Type</t>
+          <t>200B Type сер C груз</t>
         </is>
       </c>
     </row>
@@ -2564,7 +2564,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>185B LS-2 б/к Type</t>
+          <t>185B Type LS-2 б/к</t>
         </is>
       </c>
     </row>
@@ -2581,7 +2581,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>185B груз LS-2 сер Type</t>
+          <t>185B Type LS-2 сер груз</t>
         </is>
       </c>
     </row>
@@ -2598,7 +2598,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>185B H б/к Type</t>
+          <t>185B Type H б/к</t>
         </is>
       </c>
     </row>
@@ -2615,7 +2615,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>185B груз сер H Type</t>
+          <t>185B Type сер H груз</t>
         </is>
       </c>
     </row>
@@ -2632,7 +2632,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>185B C б/к Type</t>
+          <t>185B Type б/к C</t>
         </is>
       </c>
     </row>
@@ -2649,7 +2649,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>185B груз C сер Type</t>
+          <t>185B Type сер C груз</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>185B груз LS-2 сер Type</t>
+          <t>185B Type LS-2 сер груз</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>185B груз сер H Type</t>
+          <t>185B Type сер H груз</t>
         </is>
       </c>
     </row>
@@ -2700,7 +2700,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>185B груз C сер Type</t>
+          <t>185B Type сер C груз</t>
         </is>
       </c>
     </row>
@@ -2717,7 +2717,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>груз LS-2 сер Type</t>
+          <t>Type LS-2 сер груз</t>
         </is>
       </c>
     </row>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>груз сер H Type</t>
+          <t>Type сер H груз</t>
         </is>
       </c>
     </row>
@@ -2751,7 +2751,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>груз C сер Type</t>
+          <t>Type сер C груз</t>
         </is>
       </c>
     </row>
@@ -2768,7 +2768,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>груз LS-2 сер Type</t>
+          <t>Type LS-2 сер груз</t>
         </is>
       </c>
     </row>
@@ -2785,7 +2785,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>груз сер H Type</t>
+          <t>Type сер H груз</t>
         </is>
       </c>
     </row>
@@ -2802,7 +2802,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>груз C сер Type</t>
+          <t>Type сер C груз</t>
         </is>
       </c>
     </row>
@@ -2819,7 +2819,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>168B груз сер</t>
+          <t>168B сер груз</t>
         </is>
       </c>
     </row>
@@ -2917,7 +2917,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>165A8 сер сх б/к</t>
+          <t>165A8 сер б/к сх</t>
         </is>
       </c>
     </row>
@@ -3546,7 +3546,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>141A8 сер сх б/к</t>
+          <t>141A8 сер б/к сх</t>
         </is>
       </c>
     </row>
@@ -3648,7 +3648,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>сер сх б/к</t>
+          <t>сер б/к сх</t>
         </is>
       </c>
     </row>
@@ -4532,7 +4532,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>104A6 вен.161 сер сх</t>
+          <t>104A6 сер сх вен.161</t>
         </is>
       </c>
     </row>
@@ -4549,7 +4549,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>104A6 вен.161 сер</t>
+          <t>104A6 сер вен.161</t>
         </is>
       </c>
     </row>
@@ -4583,7 +4583,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>сер сх L-2</t>
+          <t>сер L-2 сх</t>
         </is>
       </c>
     </row>
@@ -4617,7 +4617,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>сер сх L-2</t>
+          <t>сер L-2 сх</t>
         </is>
       </c>
     </row>
@@ -4634,7 +4634,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>вен.161 сер сх</t>
+          <t>сер сх вен.161</t>
         </is>
       </c>
     </row>
@@ -4736,7 +4736,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>вен.161 сер сх</t>
+          <t>сер сх вен.161</t>
         </is>
       </c>
     </row>
@@ -5399,7 +5399,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>вен.161 сер легк</t>
+          <t>легк сер вен.161</t>
         </is>
       </c>
     </row>
@@ -5433,7 +5433,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>груз камневыт сер</t>
+          <t>сер груз камневыт</t>
         </is>
       </c>
     </row>
@@ -5450,7 +5450,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>груз сер</t>
+          <t>сер груз</t>
         </is>
       </c>
     </row>
@@ -5467,7 +5467,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>груз сер</t>
+          <t>сер груз</t>
         </is>
       </c>
     </row>
@@ -5484,7 +5484,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>груз сер</t>
+          <t>сер груз</t>
         </is>
       </c>
     </row>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>груз сер</t>
+          <t>сер груз</t>
         </is>
       </c>
     </row>
@@ -5518,7 +5518,7 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>156L груз сер</t>
+          <t>156L сер груз</t>
         </is>
       </c>
     </row>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>16 груз сер</t>
+          <t>16 сер груз</t>
         </is>
       </c>
     </row>
@@ -5552,7 +5552,7 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>18 груз сер</t>
+          <t>18 сер груз</t>
         </is>
       </c>
     </row>
@@ -5569,7 +5569,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>18 груз сер</t>
+          <t>18 сер груз</t>
         </is>
       </c>
     </row>
@@ -5586,7 +5586,7 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>18 груз сер</t>
+          <t>18 сер груз</t>
         </is>
       </c>
     </row>
@@ -5603,7 +5603,7 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>груз сер</t>
+          <t>сер груз</t>
         </is>
       </c>
     </row>
@@ -5620,7 +5620,7 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>груз сер</t>
+          <t>сер груз</t>
         </is>
       </c>
     </row>
@@ -5637,7 +5637,7 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>груз сер</t>
+          <t>сер груз</t>
         </is>
       </c>
     </row>
@@ -5654,7 +5654,7 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>груз сер</t>
+          <t>сер груз</t>
         </is>
       </c>
     </row>
@@ -5671,7 +5671,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>груз сер</t>
+          <t>сер груз</t>
         </is>
       </c>
     </row>
@@ -5688,7 +5688,7 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>16 груз сер</t>
+          <t>16 сер груз</t>
         </is>
       </c>
     </row>
@@ -5705,7 +5705,7 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>18 груз сер</t>
+          <t>18 сер груз</t>
         </is>
       </c>
     </row>
@@ -5722,7 +5722,7 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>18 груз сер</t>
+          <t>18 сер груз</t>
         </is>
       </c>
     </row>
@@ -5739,7 +5739,7 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>16 груз сер</t>
+          <t>16 сер груз</t>
         </is>
       </c>
     </row>
@@ -5756,7 +5756,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>груз сер</t>
+          <t>сер груз</t>
         </is>
       </c>
     </row>
@@ -5773,7 +5773,7 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>груз сер</t>
+          <t>сер груз</t>
         </is>
       </c>
     </row>
@@ -5790,7 +5790,7 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>груз сер</t>
+          <t>сер груз</t>
         </is>
       </c>
     </row>
@@ -5807,7 +5807,7 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>14 груз сер</t>
+          <t>14 сер груз</t>
         </is>
       </c>
     </row>
@@ -5824,7 +5824,7 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>12 груз сер</t>
+          <t>12 сер груз</t>
         </is>
       </c>
     </row>
@@ -5841,7 +5841,7 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>14 груз сер</t>
+          <t>14 сер груз</t>
         </is>
       </c>
     </row>
@@ -5858,7 +5858,7 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>10 груз сер</t>
+          <t>10 сер груз</t>
         </is>
       </c>
     </row>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>12 груз сер</t>
+          <t>12 сер груз</t>
         </is>
       </c>
     </row>
@@ -5892,7 +5892,7 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>груз сер</t>
+          <t>сер груз</t>
         </is>
       </c>
     </row>
@@ -5909,7 +5909,7 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>груз сер</t>
+          <t>сер груз</t>
         </is>
       </c>
     </row>
@@ -5926,7 +5926,7 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>груз сер</t>
+          <t>сер груз</t>
         </is>
       </c>
     </row>
@@ -5943,7 +5943,7 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>груз сер</t>
+          <t>сер груз</t>
         </is>
       </c>
     </row>
@@ -5960,7 +5960,7 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>груз сер</t>
+          <t>сер груз</t>
         </is>
       </c>
     </row>
@@ -5977,7 +5977,7 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>груз сер</t>
+          <t>сер груз</t>
         </is>
       </c>
     </row>
@@ -5994,7 +5994,7 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>груз сер</t>
+          <t>сер груз</t>
         </is>
       </c>
     </row>
@@ -6011,7 +6011,7 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>груз сер</t>
+          <t>сер груз</t>
         </is>
       </c>
     </row>
@@ -6028,7 +6028,7 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>16 груз сер</t>
+          <t>16 сер груз</t>
         </is>
       </c>
     </row>
@@ -6045,7 +6045,7 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>груз камневыт сер</t>
+          <t>сер груз камневыт</t>
         </is>
       </c>
     </row>
@@ -6062,7 +6062,7 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>152K груз сер</t>
+          <t>152K сер груз</t>
         </is>
       </c>
     </row>
@@ -6079,7 +6079,7 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>груз сер</t>
+          <t>сер груз</t>
         </is>
       </c>
     </row>
@@ -6096,7 +6096,7 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>груз сер</t>
+          <t>сер груз</t>
         </is>
       </c>
     </row>
@@ -6113,7 +6113,7 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>груз сер</t>
+          <t>сер груз</t>
         </is>
       </c>
     </row>
@@ -6130,7 +6130,7 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>груз сер</t>
+          <t>сер груз</t>
         </is>
       </c>
     </row>
@@ -6147,7 +6147,7 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>груз сер б/к</t>
+          <t>сер б/к груз</t>
         </is>
       </c>
     </row>
@@ -6164,7 +6164,7 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>груз сер</t>
+          <t>сер груз</t>
         </is>
       </c>
     </row>
@@ -6181,7 +6181,7 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>груз сер</t>
+          <t>сер груз</t>
         </is>
       </c>
     </row>
@@ -6198,7 +6198,7 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>груз сер</t>
+          <t>сер груз</t>
         </is>
       </c>
     </row>
@@ -6215,7 +6215,7 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>груз сер</t>
+          <t>сер груз</t>
         </is>
       </c>
     </row>
@@ -6232,7 +6232,7 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>груз сер</t>
+          <t>сер груз</t>
         </is>
       </c>
     </row>
@@ -6249,7 +6249,7 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>груз сер б/к</t>
+          <t>сер б/к груз</t>
         </is>
       </c>
     </row>
@@ -6266,7 +6266,7 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>груз сер</t>
+          <t>сер груз</t>
         </is>
       </c>
     </row>
@@ -6283,7 +6283,7 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>груз сер б/к</t>
+          <t>сер б/к груз</t>
         </is>
       </c>
     </row>
@@ -6300,7 +6300,7 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>груз сер</t>
+          <t>сер груз</t>
         </is>
       </c>
     </row>
@@ -6317,7 +6317,7 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>груз сер</t>
+          <t>сер груз</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>вен.161 сер сх</t>
+          <t>сер сх вен.161</t>
         </is>
       </c>
     </row>
@@ -6436,7 +6436,7 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>сер легк б/к</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -6453,7 +6453,7 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>сер легк б/к</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -6470,7 +6470,7 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>сер легк б/к</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -6487,7 +6487,7 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>сер легк б/к</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -6504,7 +6504,7 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>сер легк</t>
+          <t>легк сер</t>
         </is>
       </c>
     </row>
@@ -6521,7 +6521,7 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>сер легк б/к</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -6538,7 +6538,7 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>сер легк б/к</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -6555,7 +6555,7 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>сер ошип</t>
+          <t>ошип сер</t>
         </is>
       </c>
     </row>
@@ -6572,7 +6572,7 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>сер легк б/к</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -6589,7 +6589,7 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>сер ошип</t>
+          <t>ошип сер</t>
         </is>
       </c>
     </row>
@@ -6606,7 +6606,7 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>сер легк б/к</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -6623,7 +6623,7 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>сер легк б/к</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -6640,7 +6640,7 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>сер легк б/к</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -6657,7 +6657,7 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>сер ошип</t>
+          <t>ошип сер</t>
         </is>
       </c>
     </row>
@@ -6674,7 +6674,7 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>сер легк б/к</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -6691,7 +6691,7 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>сер легк б/к</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -6708,7 +6708,7 @@
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>сер легк б/к</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>сер легк б/к</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -6742,7 +6742,7 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>сер легк б/к</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -6759,7 +6759,7 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>сер легк б/к</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -6776,7 +6776,7 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>сер легк</t>
+          <t>легк сер</t>
         </is>
       </c>
     </row>
@@ -6810,7 +6810,7 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>сер легк б/к</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -6827,7 +6827,7 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>сер легк</t>
+          <t>легк сер</t>
         </is>
       </c>
     </row>
@@ -6844,7 +6844,7 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>сер легк б/к</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -6861,7 +6861,7 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>сер ошип</t>
+          <t>ошип сер</t>
         </is>
       </c>
     </row>
@@ -6878,7 +6878,7 @@
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>сер легк б/к</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -6895,7 +6895,7 @@
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>сер легк</t>
+          <t>легк сер</t>
         </is>
       </c>
     </row>
@@ -6912,7 +6912,7 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>сер легк б/к</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -6929,7 +6929,7 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>сер ошип</t>
+          <t>ошип сер</t>
         </is>
       </c>
     </row>
@@ -6946,7 +6946,7 @@
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>сер легк б/к</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -6963,7 +6963,7 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>сер легк б/к</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>сер легк б/к</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -6997,7 +6997,7 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>сер легк</t>
+          <t>легк сер</t>
         </is>
       </c>
     </row>
@@ -7014,7 +7014,7 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>сер легк б/к</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -7031,7 +7031,7 @@
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>сер легк б/к</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -7048,7 +7048,7 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>сер ошип</t>
+          <t>ошип сер</t>
         </is>
       </c>
     </row>
@@ -7065,7 +7065,7 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>сер легк б/к</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -7082,7 +7082,7 @@
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>сер легк б/к</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -7099,7 +7099,7 @@
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>сер легк б/к</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -7116,7 +7116,7 @@
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>сер легк б/к</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -7133,7 +7133,7 @@
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>сер легк</t>
+          <t>легк сер</t>
         </is>
       </c>
     </row>
@@ -7150,7 +7150,7 @@
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>сер легк б/к</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -7167,7 +7167,7 @@
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>сер легк б/к</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>сер легк б/к</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -7201,7 +7201,7 @@
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>сер легк б/к</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -7218,7 +7218,7 @@
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>сер ошип</t>
+          <t>ошип сер</t>
         </is>
       </c>
     </row>
@@ -7235,7 +7235,7 @@
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>сер легк б/к</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -7252,7 +7252,7 @@
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>сер легк б/к</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -7269,7 +7269,7 @@
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>сер ошип</t>
+          <t>ошип сер</t>
         </is>
       </c>
     </row>
@@ -7286,7 +7286,7 @@
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>сер легк б/к</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -7303,7 +7303,7 @@
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>сер легк б/к</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -7320,7 +7320,7 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>сер легк б/к</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -7337,7 +7337,7 @@
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>сер ошип</t>
+          <t>ошип сер</t>
         </is>
       </c>
     </row>
@@ -7354,7 +7354,7 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>сер легк б/к</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -7371,7 +7371,7 @@
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>сер легк б/к</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -7388,7 +7388,7 @@
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>сер легк б/к</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -7405,7 +7405,7 @@
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>сер легк б/к</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -7422,7 +7422,7 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>сер легк б/к</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -7439,7 +7439,7 @@
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>сер легк б/к</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -7456,7 +7456,7 @@
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>сер легк б/к</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -7473,7 +7473,7 @@
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>сер легк б/к</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -7490,7 +7490,7 @@
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>сер легк б/к</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -7507,7 +7507,7 @@
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>сер легк б/к</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -7524,7 +7524,7 @@
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>сер легк б/к</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -7541,7 +7541,7 @@
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>сер легк б/к</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -7558,7 +7558,7 @@
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>сер легк б/к</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -7575,7 +7575,7 @@
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>сер легк б/к</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -7592,7 +7592,7 @@
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>сер легк б/к</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -7609,7 +7609,7 @@
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>сер ошип</t>
+          <t>ошип сер</t>
         </is>
       </c>
     </row>
@@ -7626,7 +7626,7 @@
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>сер легк б/к</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -7643,7 +7643,7 @@
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>сер легк б/к</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -7660,7 +7660,7 @@
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>сер легк б/к</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -7677,7 +7677,7 @@
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>сер легк б/к</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -7694,7 +7694,7 @@
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>сер легк б/к</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -7711,7 +7711,7 @@
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>сер легк б/к</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>сер легк б/к</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -7745,7 +7745,7 @@
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>сер легк б/к</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -7762,7 +7762,7 @@
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>сер легк б/к</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -7779,7 +7779,7 @@
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>сер ошип</t>
+          <t>ошип сер</t>
         </is>
       </c>
     </row>
@@ -7796,7 +7796,7 @@
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>сер легк б/к</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -7813,7 +7813,7 @@
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>сер легк б/к</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -7830,7 +7830,7 @@
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>сер легк б/к</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -7847,7 +7847,7 @@
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>сер легк б/к</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -7864,7 +7864,7 @@
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>сер легк б/к</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -7881,7 +7881,7 @@
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>сер легк б/к</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -7898,7 +7898,7 @@
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>сер легк б/к</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -7915,7 +7915,7 @@
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>сер легк б/к</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -7932,7 +7932,7 @@
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>сер легк б/к</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -7949,7 +7949,7 @@
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>сер легк б/к</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -7966,7 +7966,7 @@
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>сер легк б/к</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -7983,7 +7983,7 @@
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>сер легк б/к</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -8000,7 +8000,7 @@
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>сер легк</t>
+          <t>легк сер</t>
         </is>
       </c>
     </row>
@@ -8017,7 +8017,7 @@
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>сер легк б/к</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -8034,7 +8034,7 @@
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>сер легк б/к</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -8051,7 +8051,7 @@
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>сер легк б/к</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -8068,7 +8068,7 @@
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>сер легк б/к</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -8085,7 +8085,7 @@
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>сер легк б/к</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -8102,7 +8102,7 @@
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>сер легк б/к</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -8119,7 +8119,7 @@
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>сер легк б/к</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -8136,7 +8136,7 @@
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>сер легк б/к</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -8153,7 +8153,7 @@
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>сер легк б/к</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -8170,7 +8170,7 @@
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>сер л/г б/к</t>
+          <t>сер б/к л/г</t>
         </is>
       </c>
     </row>
@@ -8187,7 +8187,7 @@
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>сер л/г б/к</t>
+          <t>сер б/к л/г</t>
         </is>
       </c>
     </row>
@@ -8204,7 +8204,7 @@
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>сер л/г б/к</t>
+          <t>сер б/к л/г</t>
         </is>
       </c>
     </row>
@@ -8221,7 +8221,7 @@
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>сер л/г б/к</t>
+          <t>сер б/к л/г</t>
         </is>
       </c>
     </row>
@@ -8306,7 +8306,7 @@
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>сер л/г б/к</t>
+          <t>сер б/к л/г</t>
         </is>
       </c>
     </row>
@@ -8391,7 +8391,7 @@
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>сер ошип</t>
+          <t>ошип сер</t>
         </is>
       </c>
     </row>
@@ -8425,7 +8425,7 @@
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>сер л/г б/к</t>
+          <t>сер б/к л/г</t>
         </is>
       </c>
     </row>
@@ -8476,7 +8476,7 @@
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>сер легк б/к</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -8493,7 +8493,7 @@
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>68 груз сер</t>
+          <t>68 сер груз</t>
         </is>
       </c>
     </row>
@@ -8510,7 +8510,7 @@
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>68 груз сер</t>
+          <t>68 сер груз</t>
         </is>
       </c>
     </row>
@@ -8527,7 +8527,7 @@
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>58 груз сер</t>
+          <t>58 сер груз</t>
         </is>
       </c>
     </row>
@@ -8544,7 +8544,7 @@
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>58 груз сер</t>
+          <t>58 сер груз</t>
         </is>
       </c>
     </row>
@@ -8561,7 +8561,7 @@
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>54 груз сер</t>
+          <t>54 сер груз</t>
         </is>
       </c>
     </row>
@@ -8578,7 +8578,7 @@
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>48 груз сер</t>
+          <t>48 сер груз</t>
         </is>
       </c>
     </row>
@@ -8595,7 +8595,7 @@
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>48 груз сер</t>
+          <t>48 сер груз</t>
         </is>
       </c>
     </row>
@@ -8612,7 +8612,7 @@
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>груз LS-2 сер Type</t>
+          <t>Type LS-2 сер груз</t>
         </is>
       </c>
     </row>
@@ -8629,7 +8629,7 @@
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>груз сер H Type</t>
+          <t>Type сер H груз</t>
         </is>
       </c>
     </row>
@@ -8646,7 +8646,7 @@
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>груз C сер Type</t>
+          <t>Type сер C груз</t>
         </is>
       </c>
     </row>
@@ -8663,7 +8663,7 @@
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>210B LS-2 сер Type</t>
+          <t>210B Type LS-2 сер</t>
         </is>
       </c>
     </row>
@@ -8680,7 +8680,7 @@
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>210B сер H Type</t>
+          <t>210B Type сер H</t>
         </is>
       </c>
     </row>
@@ -8697,7 +8697,7 @@
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>210B C сер Type</t>
+          <t>210B Type сер C</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>груз LS-2 сер Type</t>
+          <t>Type LS-2 сер груз</t>
         </is>
       </c>
     </row>
@@ -8731,7 +8731,7 @@
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>груз сер H Type</t>
+          <t>Type сер H груз</t>
         </is>
       </c>
     </row>
@@ -8748,7 +8748,7 @@
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>груз C сер Type</t>
+          <t>Type сер C груз</t>
         </is>
       </c>
     </row>
@@ -8765,7 +8765,7 @@
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>202B LS-2 сер Type</t>
+          <t>202B Type LS-2 сер</t>
         </is>
       </c>
     </row>
@@ -8782,7 +8782,7 @@
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>202B сер H Type</t>
+          <t>202B Type сер H</t>
         </is>
       </c>
     </row>
@@ -8799,7 +8799,7 @@
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>202B C сер Type</t>
+          <t>202B Type сер C</t>
         </is>
       </c>
     </row>
@@ -8816,7 +8816,7 @@
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>202B LS-2 сер Type</t>
+          <t>202B Type LS-2 сер</t>
         </is>
       </c>
     </row>
@@ -8833,7 +8833,7 @@
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>202B сер H Type</t>
+          <t>202B Type сер H</t>
         </is>
       </c>
     </row>
@@ -8850,7 +8850,7 @@
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>202B C сер Type</t>
+          <t>202B Type сер C</t>
         </is>
       </c>
     </row>
@@ -8867,7 +8867,7 @@
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>груз сер</t>
+          <t>сер груз</t>
         </is>
       </c>
     </row>
@@ -8884,7 +8884,7 @@
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>груз сер б/к</t>
+          <t>сер б/к груз</t>
         </is>
       </c>
     </row>
@@ -8901,7 +8901,7 @@
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>груз сер</t>
+          <t>сер груз</t>
         </is>
       </c>
     </row>
@@ -8918,7 +8918,7 @@
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>груз сер</t>
+          <t>сер груз</t>
         </is>
       </c>
     </row>
@@ -8935,7 +8935,7 @@
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>груз сер</t>
+          <t>сер груз</t>
         </is>
       </c>
     </row>
@@ -8952,7 +8952,7 @@
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>173G груз сер б/к</t>
+          <t>173G сер б/к груз</t>
         </is>
       </c>
     </row>
@@ -8969,7 +8969,7 @@
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>173G груз сер</t>
+          <t>173G сер груз</t>
         </is>
       </c>
     </row>
@@ -8986,7 +8986,7 @@
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>173G груз сер</t>
+          <t>173G сер груз</t>
         </is>
       </c>
     </row>
@@ -9003,7 +9003,7 @@
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>173G груз сер</t>
+          <t>173G сер груз</t>
         </is>
       </c>
     </row>
@@ -9020,7 +9020,7 @@
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>173G груз сер</t>
+          <t>173G сер груз</t>
         </is>
       </c>
     </row>
@@ -9037,7 +9037,7 @@
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>173G груз сер</t>
+          <t>173G сер груз</t>
         </is>
       </c>
     </row>
@@ -9071,7 +9071,7 @@
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>168J груз сер</t>
+          <t>168J сер груз</t>
         </is>
       </c>
     </row>
@@ -9088,7 +9088,7 @@
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>груз сер б/к</t>
+          <t>сер б/к груз</t>
         </is>
       </c>
     </row>

--- a/src/Tyres.xlsx
+++ b/src/Tyres.xlsx
@@ -456,7 +456,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>42 сер груз</t>
+          <t>42 груз сер</t>
         </is>
       </c>
     </row>
@@ -473,7 +473,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>30 сер груз</t>
+          <t>30 груз сер</t>
         </is>
       </c>
     </row>
@@ -490,7 +490,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>12 сер груз</t>
+          <t>12 груз сер</t>
         </is>
       </c>
     </row>
@@ -507,7 +507,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>28 сер груз</t>
+          <t>28 груз сер</t>
         </is>
       </c>
     </row>
@@ -524,7 +524,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>28 сер б/к</t>
+          <t>28 б/к сер</t>
         </is>
       </c>
     </row>
@@ -541,7 +541,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>32 сер груз</t>
+          <t>32 груз сер</t>
         </is>
       </c>
     </row>
@@ -558,7 +558,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>32 сер б/к</t>
+          <t>32 б/к сер</t>
         </is>
       </c>
     </row>
@@ -575,7 +575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>28 сер груз</t>
+          <t>28 груз сер</t>
         </is>
       </c>
     </row>
@@ -592,7 +592,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>28 сер б/к груз</t>
+          <t>28 груз б/к сер</t>
         </is>
       </c>
     </row>
@@ -609,7 +609,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>32 сер груз</t>
+          <t>32 груз сер</t>
         </is>
       </c>
     </row>
@@ -626,7 +626,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>32 сер б/к груз</t>
+          <t>32 груз б/к сер</t>
         </is>
       </c>
     </row>
@@ -643,7 +643,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>28 сер груз</t>
+          <t>28 груз сер</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>28 сер б/к груз</t>
+          <t>28 груз б/к сер</t>
         </is>
       </c>
     </row>
@@ -677,7 +677,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>32 сер груз</t>
+          <t>32 груз сер</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>32 сер б/к груз</t>
+          <t>32 груз б/к сер</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Type LS-2 сер груз</t>
+          <t>груз Type LS-2 сер</t>
         </is>
       </c>
     </row>
@@ -728,7 +728,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Type сер H груз</t>
+          <t>груз Type сер H</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Type сер C груз</t>
+          <t>груз Type сер C</t>
         </is>
       </c>
     </row>
@@ -762,7 +762,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Type LS-2 сер груз</t>
+          <t>груз Type LS-2 сер</t>
         </is>
       </c>
     </row>
@@ -779,7 +779,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Type сер H груз</t>
+          <t>груз Type сер H</t>
         </is>
       </c>
     </row>
@@ -796,7 +796,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Type сер C груз</t>
+          <t>груз Type сер C</t>
         </is>
       </c>
     </row>
@@ -813,7 +813,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>193B Type LS-2 сер груз</t>
+          <t>193B груз Type LS-2 сер</t>
         </is>
       </c>
     </row>
@@ -830,7 +830,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>193B Type сер H груз</t>
+          <t>193B груз Type сер H</t>
         </is>
       </c>
     </row>
@@ -847,7 +847,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>193B Type сер C груз</t>
+          <t>193B груз Type сер C</t>
         </is>
       </c>
     </row>
@@ -864,7 +864,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>42 сер груз</t>
+          <t>42 груз сер</t>
         </is>
       </c>
     </row>
@@ -881,7 +881,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>205B сер груз</t>
+          <t>205B груз сер</t>
         </is>
       </c>
     </row>
@@ -915,7 +915,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>20 сер б/к груз</t>
+          <t>20 груз б/к сер</t>
         </is>
       </c>
     </row>
@@ -966,7 +966,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>24 сер б/к груз</t>
+          <t>24 груз б/к сер</t>
         </is>
       </c>
     </row>
@@ -983,7 +983,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>28 сер б/к груз</t>
+          <t>28 груз б/к сер</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>20 сер б/к груз</t>
+          <t>20 груз б/к сер</t>
         </is>
       </c>
     </row>
@@ -1017,7 +1017,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>36 сер груз</t>
+          <t>36 груз сер</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>36 сер груз</t>
+          <t>36 груз сер</t>
         </is>
       </c>
     </row>
@@ -1051,7 +1051,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>32 сер груз</t>
+          <t>32 груз сер</t>
         </is>
       </c>
     </row>
@@ -1068,7 +1068,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>12 сер груз</t>
+          <t>12 груз сер</t>
         </is>
       </c>
     </row>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>16 сер груз</t>
+          <t>16 груз сер</t>
         </is>
       </c>
     </row>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>16 сер груз</t>
+          <t>16 груз сер</t>
         </is>
       </c>
     </row>
@@ -1119,7 +1119,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>16 сер груз</t>
+          <t>16 груз сер</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>16 сер б/к</t>
+          <t>16 б/к сер</t>
         </is>
       </c>
     </row>
@@ -1153,7 +1153,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>28 сер груз</t>
+          <t>28 груз сер</t>
         </is>
       </c>
     </row>
@@ -1170,7 +1170,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>28 сер б/к</t>
+          <t>28 б/к сер</t>
         </is>
       </c>
     </row>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>28 сер груз</t>
+          <t>28 груз сер</t>
         </is>
       </c>
     </row>
@@ -1204,7 +1204,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>20 сер груз</t>
+          <t>20 груз сер</t>
         </is>
       </c>
     </row>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>170B сер груз</t>
+          <t>170B груз сер</t>
         </is>
       </c>
     </row>
@@ -1255,7 +1255,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Type LS-2 сер груз</t>
+          <t>груз Type LS-2 сер</t>
         </is>
       </c>
     </row>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Type сер H груз</t>
+          <t>груз Type сер H</t>
         </is>
       </c>
     </row>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Type сер C груз</t>
+          <t>груз Type сер C</t>
         </is>
       </c>
     </row>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>32 сер груз</t>
+          <t>32 груз сер</t>
         </is>
       </c>
     </row>
@@ -1357,7 +1357,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>32 сер груз</t>
+          <t>32 груз сер</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>40 сер груз</t>
+          <t>40 груз сер</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>32 сер б/к груз</t>
+          <t>32 груз б/к сер</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>36 сер б/к груз</t>
+          <t>36 груз б/к сер</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1442,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>28 сер б/к</t>
+          <t>28 б/к сер</t>
         </is>
       </c>
     </row>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>32 сер груз</t>
+          <t>32 груз сер</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>185B сер груз</t>
+          <t>185B груз сер</t>
         </is>
       </c>
     </row>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>185B Type LS-2 б/к</t>
+          <t>185B Type б/к LS-2</t>
         </is>
       </c>
     </row>
@@ -1527,7 +1527,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Type LS-2 сер груз</t>
+          <t>груз Type LS-2 сер</t>
         </is>
       </c>
     </row>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>185B Type H б/к</t>
+          <t>185B Type б/к H</t>
         </is>
       </c>
     </row>
@@ -1561,7 +1561,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Type сер H груз</t>
+          <t>груз Type сер H</t>
         </is>
       </c>
     </row>
@@ -1595,7 +1595,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Type сер C груз</t>
+          <t>груз Type сер C</t>
         </is>
       </c>
     </row>
@@ -1612,7 +1612,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>215A2 сер груз</t>
+          <t>215A2 груз сер</t>
         </is>
       </c>
     </row>
@@ -1663,7 +1663,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>170B сер C L-2</t>
+          <t>170B сер L-2 C</t>
         </is>
       </c>
     </row>
@@ -1680,7 +1680,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>164A2 сер груз</t>
+          <t>164A2 груз сер</t>
         </is>
       </c>
     </row>
@@ -1697,7 +1697,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>20 сер груз</t>
+          <t>20 груз сер</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>22 сер груз</t>
+          <t>22 груз сер</t>
         </is>
       </c>
     </row>
@@ -1731,7 +1731,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>12 сер груз</t>
+          <t>12 груз сер</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>12 сер б/к груз</t>
+          <t>12 груз б/к сер</t>
         </is>
       </c>
     </row>
@@ -1765,7 +1765,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>16 сер груз</t>
+          <t>16 груз сер</t>
         </is>
       </c>
     </row>
@@ -1782,7 +1782,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>16 сер б/к груз</t>
+          <t>16 груз б/к сер</t>
         </is>
       </c>
     </row>
@@ -1799,7 +1799,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>20 сер груз</t>
+          <t>20 груз сер</t>
         </is>
       </c>
     </row>
@@ -1816,7 +1816,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>20 сер б/к</t>
+          <t>20 б/к сер</t>
         </is>
       </c>
     </row>
@@ -1833,7 +1833,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>182A2 сер груз</t>
+          <t>182A2 груз сер</t>
         </is>
       </c>
     </row>
@@ -1850,7 +1850,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>182A2 LS-2 сер груз</t>
+          <t>182A2 груз LS-2 сер</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>182A2 сер H груз</t>
+          <t>182A2 груз сер H</t>
         </is>
       </c>
     </row>
@@ -1884,7 +1884,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>182A2 сер C груз</t>
+          <t>182A2 груз сер C</t>
         </is>
       </c>
     </row>
@@ -1901,7 +1901,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>182A2 LS-2 сер б/к груз</t>
+          <t>182A2 груз б/к LS-2 сер</t>
         </is>
       </c>
     </row>
@@ -1918,7 +1918,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>182A2 сер H б/к груз</t>
+          <t>182A2 груз б/к сер H</t>
         </is>
       </c>
     </row>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>182A2 сер б/к C груз</t>
+          <t>182A2 груз б/к сер C</t>
         </is>
       </c>
     </row>
@@ -1952,7 +1952,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>сер б/к груз</t>
+          <t>груз б/к сер</t>
         </is>
       </c>
     </row>
@@ -1969,7 +1969,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>182A2 LS-2 сер б/к груз</t>
+          <t>182A2 груз б/к LS-2 сер</t>
         </is>
       </c>
     </row>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>182A2 сер H б/к груз</t>
+          <t>182A2 груз б/к сер H</t>
         </is>
       </c>
     </row>
@@ -2003,7 +2003,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>182A2 сер б/к C груз</t>
+          <t>182A2 груз б/к сер C</t>
         </is>
       </c>
     </row>
@@ -2020,7 +2020,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>182A2 сер груз</t>
+          <t>182A2 груз сер</t>
         </is>
       </c>
     </row>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>182A2 LS-2 сер груз</t>
+          <t>182A2 груз LS-2 сер</t>
         </is>
       </c>
     </row>
@@ -2054,7 +2054,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>182A2 сер H груз</t>
+          <t>182A2 груз сер H</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>182A2 сер C груз</t>
+          <t>182A2 груз сер C</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>16 сер груз</t>
+          <t>16 груз сер</t>
         </is>
       </c>
     </row>
@@ -2105,7 +2105,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>18 сер груз</t>
+          <t>18 груз сер</t>
         </is>
       </c>
     </row>
@@ -2122,7 +2122,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>20 сер груз</t>
+          <t>20 груз сер</t>
         </is>
       </c>
     </row>
@@ -2139,7 +2139,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>10 сер груз</t>
+          <t>10 груз сер</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>20 сер груз</t>
+          <t>20 груз сер</t>
         </is>
       </c>
     </row>
@@ -2173,7 +2173,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>22 сер груз</t>
+          <t>22 груз сер</t>
         </is>
       </c>
     </row>
@@ -2190,7 +2190,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>10 сер груз</t>
+          <t>10 груз сер</t>
         </is>
       </c>
     </row>
@@ -2207,7 +2207,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>14 сер груз</t>
+          <t>14 груз сер</t>
         </is>
       </c>
     </row>
@@ -2224,7 +2224,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>14 сер груз</t>
+          <t>14 груз сер</t>
         </is>
       </c>
     </row>
@@ -2241,7 +2241,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>22 сер груз</t>
+          <t>22 груз сер</t>
         </is>
       </c>
     </row>
@@ -2258,7 +2258,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>188A2 сер груз</t>
+          <t>188A2 груз сер</t>
         </is>
       </c>
     </row>
@@ -2275,7 +2275,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>26 сер груз</t>
+          <t>26 груз сер</t>
         </is>
       </c>
     </row>
@@ -2292,7 +2292,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>26 сер б/к</t>
+          <t>26 б/к сер</t>
         </is>
       </c>
     </row>
@@ -2326,7 +2326,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>12 сер груз</t>
+          <t>12 груз сер</t>
         </is>
       </c>
     </row>
@@ -2343,7 +2343,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>16 сер груз</t>
+          <t>16 груз сер</t>
         </is>
       </c>
     </row>
@@ -2360,7 +2360,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>172D сер груз</t>
+          <t>172D груз сер</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2377,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>14 сер груз</t>
+          <t>14 груз сер</t>
         </is>
       </c>
     </row>
@@ -2394,7 +2394,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>176E сер груз</t>
+          <t>176E груз сер</t>
         </is>
       </c>
     </row>
@@ -2411,7 +2411,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Type LS-2 сер груз</t>
+          <t>груз Type LS-2 сер</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Type сер H груз</t>
+          <t>груз Type сер H</t>
         </is>
       </c>
     </row>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Type сер C груз</t>
+          <t>груз Type сер C</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>200B Type LS-2 сер груз</t>
+          <t>200B груз Type LS-2 сер</t>
         </is>
       </c>
     </row>
@@ -2479,7 +2479,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>200B Type сер H груз</t>
+          <t>200B груз Type сер H</t>
         </is>
       </c>
     </row>
@@ -2496,7 +2496,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>200B Type сер C груз</t>
+          <t>200B груз Type сер C</t>
         </is>
       </c>
     </row>
@@ -2513,7 +2513,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>200B Type LS-2 сер груз</t>
+          <t>200B груз Type LS-2 сер</t>
         </is>
       </c>
     </row>
@@ -2530,7 +2530,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>200B Type сер H груз</t>
+          <t>200B груз Type сер H</t>
         </is>
       </c>
     </row>
@@ -2547,7 +2547,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>200B Type сер C груз</t>
+          <t>200B груз Type сер C</t>
         </is>
       </c>
     </row>
@@ -2564,7 +2564,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>185B Type LS-2 б/к</t>
+          <t>185B Type б/к LS-2</t>
         </is>
       </c>
     </row>
@@ -2581,7 +2581,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>185B Type LS-2 сер груз</t>
+          <t>185B груз Type LS-2 сер</t>
         </is>
       </c>
     </row>
@@ -2598,7 +2598,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>185B Type H б/к</t>
+          <t>185B Type б/к H</t>
         </is>
       </c>
     </row>
@@ -2615,7 +2615,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>185B Type сер H груз</t>
+          <t>185B груз Type сер H</t>
         </is>
       </c>
     </row>
@@ -2649,7 +2649,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>185B Type сер C груз</t>
+          <t>185B груз Type сер C</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>185B Type LS-2 сер груз</t>
+          <t>185B груз Type LS-2 сер</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>185B Type сер H груз</t>
+          <t>185B груз Type сер H</t>
         </is>
       </c>
     </row>
@@ -2700,7 +2700,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>185B Type сер C груз</t>
+          <t>185B груз Type сер C</t>
         </is>
       </c>
     </row>
@@ -2717,7 +2717,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Type LS-2 сер груз</t>
+          <t>груз Type LS-2 сер</t>
         </is>
       </c>
     </row>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Type сер H груз</t>
+          <t>груз Type сер H</t>
         </is>
       </c>
     </row>
@@ -2751,7 +2751,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Type сер C груз</t>
+          <t>груз Type сер C</t>
         </is>
       </c>
     </row>
@@ -2768,7 +2768,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Type LS-2 сер груз</t>
+          <t>груз Type LS-2 сер</t>
         </is>
       </c>
     </row>
@@ -2785,7 +2785,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Type сер H груз</t>
+          <t>груз Type сер H</t>
         </is>
       </c>
     </row>
@@ -2802,7 +2802,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Type сер C груз</t>
+          <t>груз Type сер C</t>
         </is>
       </c>
     </row>
@@ -2819,7 +2819,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>168B сер груз</t>
+          <t>168B груз сер</t>
         </is>
       </c>
     </row>
@@ -2866,7 +2866,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>158A8 сер сх</t>
+          <t>158A8 сх сер</t>
         </is>
       </c>
     </row>
@@ -2883,7 +2883,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>170A6 сер сх</t>
+          <t>170A6 сх сер</t>
         </is>
       </c>
     </row>
@@ -2900,7 +2900,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>165A8 сер сх</t>
+          <t>165A8 сх сер</t>
         </is>
       </c>
     </row>
@@ -2917,7 +2917,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>165A8 сер б/к сх</t>
+          <t>165A8 б/к сх сер</t>
         </is>
       </c>
     </row>
@@ -2934,7 +2934,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>12 сер сх</t>
+          <t>12 сх сер</t>
         </is>
       </c>
     </row>
@@ -2968,7 +2968,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>12 сер сх</t>
+          <t>12 сх сер</t>
         </is>
       </c>
     </row>
@@ -2985,7 +2985,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>172A8 сер сх</t>
+          <t>172A8 сх сер</t>
         </is>
       </c>
     </row>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>12 сер сх</t>
+          <t>12 сх сер</t>
         </is>
       </c>
     </row>
@@ -3019,7 +3019,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>18 сер сх</t>
+          <t>18 сх сер</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>169A8 сер сх</t>
+          <t>169A8 сх сер</t>
         </is>
       </c>
     </row>
@@ -3053,7 +3053,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>10 сер сх</t>
+          <t>10 сх сер</t>
         </is>
       </c>
     </row>
@@ -3070,7 +3070,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>12 сер б/к</t>
+          <t>12 б/к сер</t>
         </is>
       </c>
     </row>
@@ -3087,7 +3087,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>12 сер сх</t>
+          <t>12 сх сер</t>
         </is>
       </c>
     </row>
@@ -3104,7 +3104,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>16 сер б/к</t>
+          <t>16 б/к сер</t>
         </is>
       </c>
     </row>
@@ -3121,7 +3121,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>16 сер сх</t>
+          <t>16 сх сер</t>
         </is>
       </c>
     </row>
@@ -3155,7 +3155,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>156A8 сер сх</t>
+          <t>156A8 сх сер</t>
         </is>
       </c>
     </row>
@@ -3172,7 +3172,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>167A8 сер сх</t>
+          <t>167A8 сх сер</t>
         </is>
       </c>
     </row>
@@ -3189,7 +3189,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>166A8 сер сх</t>
+          <t>166A8 сх сер</t>
         </is>
       </c>
     </row>
@@ -3206,7 +3206,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>166A8 сер сх</t>
+          <t>166A8 сх сер</t>
         </is>
       </c>
     </row>
@@ -3223,7 +3223,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>10 сер сх</t>
+          <t>10 сх сер</t>
         </is>
       </c>
     </row>
@@ -3240,7 +3240,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>12 сер сх</t>
+          <t>12 сх сер</t>
         </is>
       </c>
     </row>
@@ -3257,7 +3257,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>158D сер сх</t>
+          <t>158D сх сер</t>
         </is>
       </c>
     </row>
@@ -3274,7 +3274,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>158D сер б/к</t>
+          <t>158D б/к сер</t>
         </is>
       </c>
     </row>
@@ -3291,7 +3291,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>147A8 сер сх</t>
+          <t>147A8 сх сер</t>
         </is>
       </c>
     </row>
@@ -3308,7 +3308,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>155A8 сер сх</t>
+          <t>155A8 сх сер</t>
         </is>
       </c>
     </row>
@@ -3325,7 +3325,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>155A8 сер сх</t>
+          <t>155A8 сх сер</t>
         </is>
       </c>
     </row>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>153A8 сер сх</t>
+          <t>153A8 сх сер</t>
         </is>
       </c>
     </row>
@@ -3359,7 +3359,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>161A8 сер сх</t>
+          <t>161A8 сх сер</t>
         </is>
       </c>
     </row>
@@ -3393,7 +3393,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>146A8 сер сх</t>
+          <t>146A8 сх сер</t>
         </is>
       </c>
     </row>
@@ -3410,7 +3410,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>12 сер сх</t>
+          <t>12 сх сер</t>
         </is>
       </c>
     </row>
@@ -3427,7 +3427,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>12 сер б/к</t>
+          <t>12 б/к сер</t>
         </is>
       </c>
     </row>
@@ -3461,7 +3461,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>141A6 сер сх</t>
+          <t>141A6 сх сер</t>
         </is>
       </c>
     </row>
@@ -3478,7 +3478,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>144A8 сер сх</t>
+          <t>144A8 сх сер</t>
         </is>
       </c>
     </row>
@@ -3495,7 +3495,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>144A8 сер сх</t>
+          <t>144A8 сх сер</t>
         </is>
       </c>
     </row>
@@ -3512,7 +3512,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>12 сер сх</t>
+          <t>12 сх сер</t>
         </is>
       </c>
     </row>
@@ -3529,7 +3529,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>сер сх</t>
+          <t>сх сер</t>
         </is>
       </c>
     </row>
@@ -3546,7 +3546,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>141A8 сер б/к сх</t>
+          <t>141A8 б/к сх сер</t>
         </is>
       </c>
     </row>
@@ -3563,7 +3563,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>154A8 сер сх</t>
+          <t>154A8 сх сер</t>
         </is>
       </c>
     </row>
@@ -3580,7 +3580,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>133A8 сер сх</t>
+          <t>133A8 сх сер</t>
         </is>
       </c>
     </row>
@@ -3597,7 +3597,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>28 сер сх</t>
+          <t>28 сх сер</t>
         </is>
       </c>
     </row>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>10 сер сх</t>
+          <t>10 сх сер</t>
         </is>
       </c>
     </row>
@@ -3631,7 +3631,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>166A8 сер сх</t>
+          <t>166A8 сх сер</t>
         </is>
       </c>
     </row>
@@ -3648,7 +3648,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>сер б/к сх</t>
+          <t>б/к сх сер</t>
         </is>
       </c>
     </row>
@@ -3665,7 +3665,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>148A8 сер сх</t>
+          <t>148A8 сх сер</t>
         </is>
       </c>
     </row>
@@ -3682,7 +3682,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>166A8 сер сх</t>
+          <t>166A8 сх сер</t>
         </is>
       </c>
     </row>
@@ -3699,7 +3699,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>130A8 сер сх</t>
+          <t>130A8 сх сер</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>сер сх</t>
+          <t>сх сер</t>
         </is>
       </c>
     </row>
@@ -3767,7 +3767,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>159A8 сер сх</t>
+          <t>159A8 сх сер</t>
         </is>
       </c>
     </row>
@@ -3784,7 +3784,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>28 сер сх</t>
+          <t>28 сх сер</t>
         </is>
       </c>
     </row>
@@ -3801,7 +3801,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>сер сх</t>
+          <t>сх сер</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>28 сер сх</t>
+          <t>28 сх сер</t>
         </is>
       </c>
     </row>
@@ -3869,7 +3869,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>28 сер сх</t>
+          <t>28 сх сер</t>
         </is>
       </c>
     </row>
@@ -3886,7 +3886,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>114A8 сер б/к</t>
+          <t>114A8 б/к сер</t>
         </is>
       </c>
     </row>
@@ -3903,7 +3903,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>114A8 сер сх</t>
+          <t>114A8 сх сер</t>
         </is>
       </c>
     </row>
@@ -3920,7 +3920,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>28 сер сх</t>
+          <t>28 сх сер</t>
         </is>
       </c>
     </row>
@@ -3937,7 +3937,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>148A8 сер б/к</t>
+          <t>148A8 б/к сер</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>148A8 сер сх</t>
+          <t>148A8 сх сер</t>
         </is>
       </c>
     </row>
@@ -3971,7 +3971,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>160D сер сх</t>
+          <t>160D сх сер</t>
         </is>
       </c>
     </row>
@@ -3988,7 +3988,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>146A8 сер сх</t>
+          <t>146A8 сх сер</t>
         </is>
       </c>
     </row>
@@ -4005,7 +4005,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>10 сер сх</t>
+          <t>10 сх сер</t>
         </is>
       </c>
     </row>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>14 сер сх</t>
+          <t>14 сх сер</t>
         </is>
       </c>
     </row>
@@ -4039,7 +4039,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>149A6 сер сх</t>
+          <t>149A6 сх сер</t>
         </is>
       </c>
     </row>
@@ -4056,7 +4056,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>153A6 сер сх</t>
+          <t>153A6 сх сер</t>
         </is>
       </c>
     </row>
@@ -4090,7 +4090,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>42 сер сх</t>
+          <t>42 сх сер</t>
         </is>
       </c>
     </row>
@@ -4107,7 +4107,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>28 сер сх</t>
+          <t>28 сх сер</t>
         </is>
       </c>
     </row>
@@ -4124,7 +4124,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>12 сер сх</t>
+          <t>12 сх сер</t>
         </is>
       </c>
     </row>
@@ -4141,7 +4141,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>28 сер сх</t>
+          <t>28 сх сер</t>
         </is>
       </c>
     </row>
@@ -4158,7 +4158,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>14 сер сх</t>
+          <t>14 сх сер</t>
         </is>
       </c>
     </row>
@@ -4175,7 +4175,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>сер сх</t>
+          <t>сх сер</t>
         </is>
       </c>
     </row>
@@ -4192,7 +4192,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>159D сер сх</t>
+          <t>159D сх сер</t>
         </is>
       </c>
     </row>
@@ -4209,7 +4209,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>28 сер сх</t>
+          <t>28 сх сер</t>
         </is>
       </c>
     </row>
@@ -4226,7 +4226,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>сер сх</t>
+          <t>сх сер</t>
         </is>
       </c>
     </row>
@@ -4243,7 +4243,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>129A8 сер сх</t>
+          <t>129A8 сх сер</t>
         </is>
       </c>
     </row>
@@ -4260,7 +4260,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>28 сер сх</t>
+          <t>28 сх сер</t>
         </is>
       </c>
     </row>
@@ -4277,7 +4277,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>28 сер сх</t>
+          <t>28 сх сер</t>
         </is>
       </c>
     </row>
@@ -4294,7 +4294,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>10 сер сх</t>
+          <t>10 сх сер</t>
         </is>
       </c>
     </row>
@@ -4311,7 +4311,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>14 сер сх</t>
+          <t>14 сх сер</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>28 сер сх</t>
+          <t>28 сх сер</t>
         </is>
       </c>
     </row>
@@ -4345,7 +4345,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>10 сер сх</t>
+          <t>10 сх сер</t>
         </is>
       </c>
     </row>
@@ -4362,7 +4362,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>сер сх</t>
+          <t>сх сер</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4379,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>28 сер сх</t>
+          <t>28 сх сер</t>
         </is>
       </c>
     </row>
@@ -4396,7 +4396,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>124A8 сер сх</t>
+          <t>124A8 сх сер</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>28 сер сх</t>
+          <t>28 сх сер</t>
         </is>
       </c>
     </row>
@@ -4430,7 +4430,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>10 сер сх</t>
+          <t>10 сх сер</t>
         </is>
       </c>
     </row>
@@ -4447,7 +4447,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>сер сх</t>
+          <t>сх сер</t>
         </is>
       </c>
     </row>
@@ -4464,7 +4464,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>сер сх</t>
+          <t>сх сер</t>
         </is>
       </c>
     </row>
@@ -4498,7 +4498,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>10 сер сх</t>
+          <t>10 сх сер</t>
         </is>
       </c>
     </row>
@@ -4515,7 +4515,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>10 сер сх</t>
+          <t>10 сх сер</t>
         </is>
       </c>
     </row>
@@ -4532,7 +4532,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>104A6 сер сх вен.161</t>
+          <t>104A6 сх вен.161 сер</t>
         </is>
       </c>
     </row>
@@ -4549,7 +4549,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>104A6 сер вен.161</t>
+          <t>104A6 вен.161 сер</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>сер сх</t>
+          <t>сх сер</t>
         </is>
       </c>
     </row>
@@ -4583,7 +4583,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>сер L-2 сх</t>
+          <t>сх сер L-2</t>
         </is>
       </c>
     </row>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>42 сер сх</t>
+          <t>42 сх сер</t>
         </is>
       </c>
     </row>
@@ -4617,7 +4617,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>сер L-2 сх</t>
+          <t>сх сер L-2</t>
         </is>
       </c>
     </row>
@@ -4634,7 +4634,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>сер сх вен.161</t>
+          <t>сх вен.161 сер</t>
         </is>
       </c>
     </row>
@@ -4651,7 +4651,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>42 сер сх</t>
+          <t>42 сх сер</t>
         </is>
       </c>
     </row>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>28 сер сх</t>
+          <t>28 сх сер</t>
         </is>
       </c>
     </row>
@@ -4685,7 +4685,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>12 сер сх</t>
+          <t>12 сх сер</t>
         </is>
       </c>
     </row>
@@ -4702,7 +4702,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>28 сер сх</t>
+          <t>28 сх сер</t>
         </is>
       </c>
     </row>
@@ -4719,7 +4719,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>42 сер сх</t>
+          <t>42 сх сер</t>
         </is>
       </c>
     </row>
@@ -4736,7 +4736,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>сер сх вен.161</t>
+          <t>сх вен.161 сер</t>
         </is>
       </c>
     </row>
@@ -4753,7 +4753,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>10 сер сх</t>
+          <t>10 сх сер</t>
         </is>
       </c>
     </row>
@@ -4787,7 +4787,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>126A8 сер сх</t>
+          <t>126A8 сх сер</t>
         </is>
       </c>
     </row>
@@ -4804,7 +4804,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>167A8 сер б/к</t>
+          <t>167A8 б/к сер</t>
         </is>
       </c>
     </row>
@@ -4821,7 +4821,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>167A8 сер сх</t>
+          <t>167A8 сх сер</t>
         </is>
       </c>
     </row>
@@ -4838,7 +4838,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>178A8 сер сх</t>
+          <t>178A8 сх сер</t>
         </is>
       </c>
     </row>
@@ -4855,7 +4855,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>178A8 сер б/к</t>
+          <t>178A8 б/к сер</t>
         </is>
       </c>
     </row>
@@ -4872,7 +4872,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>188A8 сер сх</t>
+          <t>188A8 сх сер</t>
         </is>
       </c>
     </row>
@@ -4889,7 +4889,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>180A8 сер сх</t>
+          <t>180A8 сх сер</t>
         </is>
       </c>
     </row>
@@ -4906,7 +4906,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>151D сер сх</t>
+          <t>151D сх сер</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>151D сер сх</t>
+          <t>151D сх сер</t>
         </is>
       </c>
     </row>
@@ -4957,7 +4957,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>154A8 сер сх</t>
+          <t>154A8 сх сер</t>
         </is>
       </c>
     </row>
@@ -4974,7 +4974,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>162A8 сер сх</t>
+          <t>162A8 сх сер</t>
         </is>
       </c>
     </row>
@@ -5008,7 +5008,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>168A8 сер б/к</t>
+          <t>168A8 б/к сер</t>
         </is>
       </c>
     </row>
@@ -5025,7 +5025,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>174A8 сер сх</t>
+          <t>174A8 сх сер</t>
         </is>
       </c>
     </row>
@@ -5042,7 +5042,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>16 сер сх</t>
+          <t>16 сх сер</t>
         </is>
       </c>
     </row>
@@ -5059,7 +5059,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>20 сер сх</t>
+          <t>20 сх сер</t>
         </is>
       </c>
     </row>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>24 сер сх</t>
+          <t>24 сх сер</t>
         </is>
       </c>
     </row>
@@ -5093,7 +5093,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>166D сер сх</t>
+          <t>166D сх сер</t>
         </is>
       </c>
     </row>
@@ -5110,7 +5110,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>173D сер сх</t>
+          <t>173D сх сер</t>
         </is>
       </c>
     </row>
@@ -5127,7 +5127,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>101A6 сер сх</t>
+          <t>101A6 сх сер</t>
         </is>
       </c>
     </row>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>150A8 сер сх</t>
+          <t>150A8 сх сер</t>
         </is>
       </c>
     </row>
@@ -5161,7 +5161,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>150A8 сер б/к</t>
+          <t>150A8 б/к сер</t>
         </is>
       </c>
     </row>
@@ -5195,7 +5195,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>28 сер сх</t>
+          <t>28 сх сер</t>
         </is>
       </c>
     </row>
@@ -5399,7 +5399,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>легк сер вен.161</t>
+          <t>легк вен.161 сер</t>
         </is>
       </c>
     </row>
@@ -5433,7 +5433,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>сер груз камневыт</t>
+          <t>груз камневыт сер</t>
         </is>
       </c>
     </row>
@@ -5450,7 +5450,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>сер груз</t>
+          <t>груз сер</t>
         </is>
       </c>
     </row>
@@ -5467,7 +5467,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>сер груз</t>
+          <t>груз сер</t>
         </is>
       </c>
     </row>
@@ -5484,7 +5484,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>сер груз</t>
+          <t>груз сер</t>
         </is>
       </c>
     </row>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>сер груз</t>
+          <t>груз сер</t>
         </is>
       </c>
     </row>
@@ -5518,7 +5518,7 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>156L сер груз</t>
+          <t>156L груз сер</t>
         </is>
       </c>
     </row>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>16 сер груз</t>
+          <t>16 груз сер</t>
         </is>
       </c>
     </row>
@@ -5552,7 +5552,7 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>18 сер груз</t>
+          <t>18 груз сер</t>
         </is>
       </c>
     </row>
@@ -5569,7 +5569,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>18 сер груз</t>
+          <t>18 груз сер</t>
         </is>
       </c>
     </row>
@@ -5586,7 +5586,7 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>18 сер груз</t>
+          <t>18 груз сер</t>
         </is>
       </c>
     </row>
@@ -5603,7 +5603,7 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>сер груз</t>
+          <t>груз сер</t>
         </is>
       </c>
     </row>
@@ -5620,7 +5620,7 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>сер груз</t>
+          <t>груз сер</t>
         </is>
       </c>
     </row>
@@ -5637,7 +5637,7 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>сер груз</t>
+          <t>груз сер</t>
         </is>
       </c>
     </row>
@@ -5654,7 +5654,7 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>сер груз</t>
+          <t>груз сер</t>
         </is>
       </c>
     </row>
@@ -5671,7 +5671,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>сер груз</t>
+          <t>груз сер</t>
         </is>
       </c>
     </row>
@@ -5688,7 +5688,7 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>16 сер груз</t>
+          <t>16 груз сер</t>
         </is>
       </c>
     </row>
@@ -5705,7 +5705,7 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>18 сер груз</t>
+          <t>18 груз сер</t>
         </is>
       </c>
     </row>
@@ -5722,7 +5722,7 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>18 сер груз</t>
+          <t>18 груз сер</t>
         </is>
       </c>
     </row>
@@ -5739,7 +5739,7 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>16 сер груз</t>
+          <t>16 груз сер</t>
         </is>
       </c>
     </row>
@@ -5756,7 +5756,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>сер груз</t>
+          <t>груз сер</t>
         </is>
       </c>
     </row>
@@ -5773,7 +5773,7 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>сер груз</t>
+          <t>груз сер</t>
         </is>
       </c>
     </row>
@@ -5790,7 +5790,7 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>сер груз</t>
+          <t>груз сер</t>
         </is>
       </c>
     </row>
@@ -5807,7 +5807,7 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>14 сер груз</t>
+          <t>14 груз сер</t>
         </is>
       </c>
     </row>
@@ -5824,7 +5824,7 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>12 сер груз</t>
+          <t>12 груз сер</t>
         </is>
       </c>
     </row>
@@ -5841,7 +5841,7 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>14 сер груз</t>
+          <t>14 груз сер</t>
         </is>
       </c>
     </row>
@@ -5858,7 +5858,7 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>10 сер груз</t>
+          <t>10 груз сер</t>
         </is>
       </c>
     </row>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>12 сер груз</t>
+          <t>12 груз сер</t>
         </is>
       </c>
     </row>
@@ -5892,7 +5892,7 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>сер груз</t>
+          <t>груз сер</t>
         </is>
       </c>
     </row>
@@ -5909,7 +5909,7 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>сер груз</t>
+          <t>груз сер</t>
         </is>
       </c>
     </row>
@@ -5926,7 +5926,7 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>сер груз</t>
+          <t>груз сер</t>
         </is>
       </c>
     </row>
@@ -5943,7 +5943,7 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>сер груз</t>
+          <t>груз сер</t>
         </is>
       </c>
     </row>
@@ -5960,7 +5960,7 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>сер груз</t>
+          <t>груз сер</t>
         </is>
       </c>
     </row>
@@ -5977,7 +5977,7 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>сер груз</t>
+          <t>груз сер</t>
         </is>
       </c>
     </row>
@@ -5994,7 +5994,7 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>сер груз</t>
+          <t>груз сер</t>
         </is>
       </c>
     </row>
@@ -6011,7 +6011,7 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>сер груз</t>
+          <t>груз сер</t>
         </is>
       </c>
     </row>
@@ -6028,7 +6028,7 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>16 сер груз</t>
+          <t>16 груз сер</t>
         </is>
       </c>
     </row>
@@ -6045,7 +6045,7 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>сер груз камневыт</t>
+          <t>груз камневыт сер</t>
         </is>
       </c>
     </row>
@@ -6062,7 +6062,7 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>152K сер груз</t>
+          <t>152K груз сер</t>
         </is>
       </c>
     </row>
@@ -6079,7 +6079,7 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>сер груз</t>
+          <t>груз сер</t>
         </is>
       </c>
     </row>
@@ -6096,7 +6096,7 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>сер груз</t>
+          <t>груз сер</t>
         </is>
       </c>
     </row>
@@ -6113,7 +6113,7 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>сер груз</t>
+          <t>груз сер</t>
         </is>
       </c>
     </row>
@@ -6130,7 +6130,7 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>сер груз</t>
+          <t>груз сер</t>
         </is>
       </c>
     </row>
@@ -6147,7 +6147,7 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>сер б/к груз</t>
+          <t>груз б/к сер</t>
         </is>
       </c>
     </row>
@@ -6164,7 +6164,7 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>сер груз</t>
+          <t>груз сер</t>
         </is>
       </c>
     </row>
@@ -6181,7 +6181,7 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>сер груз</t>
+          <t>груз сер</t>
         </is>
       </c>
     </row>
@@ -6198,7 +6198,7 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>сер груз</t>
+          <t>груз сер</t>
         </is>
       </c>
     </row>
@@ -6215,7 +6215,7 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>сер груз</t>
+          <t>груз сер</t>
         </is>
       </c>
     </row>
@@ -6232,7 +6232,7 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>сер груз</t>
+          <t>груз сер</t>
         </is>
       </c>
     </row>
@@ -6249,7 +6249,7 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>сер б/к груз</t>
+          <t>груз б/к сер</t>
         </is>
       </c>
     </row>
@@ -6266,7 +6266,7 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>сер груз</t>
+          <t>груз сер</t>
         </is>
       </c>
     </row>
@@ -6283,7 +6283,7 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>сер б/к груз</t>
+          <t>груз б/к сер</t>
         </is>
       </c>
     </row>
@@ -6300,7 +6300,7 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>сер груз</t>
+          <t>груз сер</t>
         </is>
       </c>
     </row>
@@ -6317,7 +6317,7 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>сер груз</t>
+          <t>груз сер</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>сер сх вен.161</t>
+          <t>сх вен.161 сер</t>
         </is>
       </c>
     </row>
@@ -6351,7 +6351,7 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>102A8 сер сх</t>
+          <t>102A8 сх сер</t>
         </is>
       </c>
     </row>
@@ -6368,7 +6368,7 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>сер сх</t>
+          <t>сх сер</t>
         </is>
       </c>
     </row>
@@ -6385,7 +6385,7 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>сер сх</t>
+          <t>сх сер</t>
         </is>
       </c>
     </row>
@@ -6402,7 +6402,7 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>сер сх</t>
+          <t>сх сер</t>
         </is>
       </c>
     </row>
@@ -6419,7 +6419,7 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>сер сх</t>
+          <t>сх сер</t>
         </is>
       </c>
     </row>
@@ -6436,7 +6436,7 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>легк сер б/к</t>
+          <t>легк б/к сер</t>
         </is>
       </c>
     </row>
@@ -6453,7 +6453,7 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>легк сер б/к</t>
+          <t>легк б/к сер</t>
         </is>
       </c>
     </row>
@@ -6470,7 +6470,7 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>легк сер б/к</t>
+          <t>легк б/к сер</t>
         </is>
       </c>
     </row>
@@ -6487,7 +6487,7 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>легк сер б/к</t>
+          <t>легк б/к сер</t>
         </is>
       </c>
     </row>
@@ -6521,7 +6521,7 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>легк сер б/к</t>
+          <t>легк б/к сер</t>
         </is>
       </c>
     </row>
@@ -6538,7 +6538,7 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>легк сер б/к</t>
+          <t>легк б/к сер</t>
         </is>
       </c>
     </row>
@@ -6572,7 +6572,7 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>легк сер б/к</t>
+          <t>легк б/к сер</t>
         </is>
       </c>
     </row>
@@ -6606,7 +6606,7 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>легк сер б/к</t>
+          <t>легк б/к сер</t>
         </is>
       </c>
     </row>
@@ -6623,7 +6623,7 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>легк сер б/к</t>
+          <t>легк б/к сер</t>
         </is>
       </c>
     </row>
@@ -6640,7 +6640,7 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>легк сер б/к</t>
+          <t>легк б/к сер</t>
         </is>
       </c>
     </row>
@@ -6674,7 +6674,7 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>легк сер б/к</t>
+          <t>легк б/к сер</t>
         </is>
       </c>
     </row>
@@ -6691,7 +6691,7 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>легк сер б/к</t>
+          <t>легк б/к сер</t>
         </is>
       </c>
     </row>
@@ -6708,7 +6708,7 @@
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>легк сер б/к</t>
+          <t>легк б/к сер</t>
         </is>
       </c>
     </row>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>легк сер б/к</t>
+          <t>легк б/к сер</t>
         </is>
       </c>
     </row>
@@ -6742,7 +6742,7 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>легк сер б/к</t>
+          <t>легк б/к сер</t>
         </is>
       </c>
     </row>
@@ -6759,7 +6759,7 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>легк сер б/к</t>
+          <t>легк б/к сер</t>
         </is>
       </c>
     </row>
@@ -6793,7 +6793,7 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>сер б/к</t>
+          <t>б/к сер</t>
         </is>
       </c>
     </row>
@@ -6810,7 +6810,7 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>легк сер б/к</t>
+          <t>легк б/к сер</t>
         </is>
       </c>
     </row>
@@ -6844,7 +6844,7 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>легк сер б/к</t>
+          <t>легк б/к сер</t>
         </is>
       </c>
     </row>
@@ -6878,7 +6878,7 @@
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>легк сер б/к</t>
+          <t>легк б/к сер</t>
         </is>
       </c>
     </row>
@@ -6912,7 +6912,7 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>легк сер б/к</t>
+          <t>легк б/к сер</t>
         </is>
       </c>
     </row>
@@ -6946,7 +6946,7 @@
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>легк сер б/к</t>
+          <t>легк б/к сер</t>
         </is>
       </c>
     </row>
@@ -6963,7 +6963,7 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>легк сер б/к</t>
+          <t>легк б/к сер</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>легк сер б/к</t>
+          <t>легк б/к сер</t>
         </is>
       </c>
     </row>
@@ -7014,7 +7014,7 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>легк сер б/к</t>
+          <t>легк б/к сер</t>
         </is>
       </c>
     </row>
@@ -7031,7 +7031,7 @@
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>легк сер б/к</t>
+          <t>легк б/к сер</t>
         </is>
       </c>
     </row>
@@ -7065,7 +7065,7 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>легк сер б/к</t>
+          <t>легк б/к сер</t>
         </is>
       </c>
     </row>
@@ -7082,7 +7082,7 @@
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>легк сер б/к</t>
+          <t>легк б/к сер</t>
         </is>
       </c>
     </row>
@@ -7099,7 +7099,7 @@
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>легк сер б/к</t>
+          <t>легк б/к сер</t>
         </is>
       </c>
     </row>
@@ -7116,7 +7116,7 @@
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>легк сер б/к</t>
+          <t>легк б/к сер</t>
         </is>
       </c>
     </row>
@@ -7150,7 +7150,7 @@
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>легк сер б/к</t>
+          <t>легк б/к сер</t>
         </is>
       </c>
     </row>
@@ -7167,7 +7167,7 @@
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>легк сер б/к</t>
+          <t>легк б/к сер</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>легк сер б/к</t>
+          <t>легк б/к сер</t>
         </is>
       </c>
     </row>
@@ -7201,7 +7201,7 @@
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>легк сер б/к</t>
+          <t>легк б/к сер</t>
         </is>
       </c>
     </row>
@@ -7235,7 +7235,7 @@
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>легк сер б/к</t>
+          <t>легк б/к сер</t>
         </is>
       </c>
     </row>
@@ -7252,7 +7252,7 @@
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>легк сер б/к</t>
+          <t>легк б/к сер</t>
         </is>
       </c>
     </row>
@@ -7286,7 +7286,7 @@
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>легк сер б/к</t>
+          <t>легк б/к сер</t>
         </is>
       </c>
     </row>
@@ -7303,7 +7303,7 @@
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>легк сер б/к</t>
+          <t>легк б/к сер</t>
         </is>
       </c>
     </row>
@@ -7320,7 +7320,7 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>легк сер б/к</t>
+          <t>легк б/к сер</t>
         </is>
       </c>
     </row>
@@ -7354,7 +7354,7 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>легк сер б/к</t>
+          <t>легк б/к сер</t>
         </is>
       </c>
     </row>
@@ -7371,7 +7371,7 @@
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>легк сер б/к</t>
+          <t>легк б/к сер</t>
         </is>
       </c>
     </row>
@@ -7388,7 +7388,7 @@
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>легк сер б/к</t>
+          <t>легк б/к сер</t>
         </is>
       </c>
     </row>
@@ -7405,7 +7405,7 @@
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>легк сер б/к</t>
+          <t>легк б/к сер</t>
         </is>
       </c>
     </row>
@@ -7422,7 +7422,7 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>легк сер б/к</t>
+          <t>легк б/к сер</t>
         </is>
       </c>
     </row>
@@ -7439,7 +7439,7 @@
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>легк сер б/к</t>
+          <t>легк б/к сер</t>
         </is>
       </c>
     </row>
@@ -7456,7 +7456,7 @@
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>легк сер б/к</t>
+          <t>легк б/к сер</t>
         </is>
       </c>
     </row>
@@ -7473,7 +7473,7 @@
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>легк сер б/к</t>
+          <t>легк б/к сер</t>
         </is>
       </c>
     </row>
@@ -7490,7 +7490,7 @@
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>легк сер б/к</t>
+          <t>легк б/к сер</t>
         </is>
       </c>
     </row>
@@ -7507,7 +7507,7 @@
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>легк сер б/к</t>
+          <t>легк б/к сер</t>
         </is>
       </c>
     </row>
@@ -7524,7 +7524,7 @@
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>легк сер б/к</t>
+          <t>легк б/к сер</t>
         </is>
       </c>
     </row>
@@ -7541,7 +7541,7 @@
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>легк сер б/к</t>
+          <t>легк б/к сер</t>
         </is>
       </c>
     </row>
@@ -7558,7 +7558,7 @@
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>легк сер б/к</t>
+          <t>легк б/к сер</t>
         </is>
       </c>
     </row>
@@ -7575,7 +7575,7 @@
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>легк сер б/к</t>
+          <t>легк б/к сер</t>
         </is>
       </c>
     </row>
@@ -7592,7 +7592,7 @@
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>легк сер б/к</t>
+          <t>легк б/к сер</t>
         </is>
       </c>
     </row>
@@ -7626,7 +7626,7 @@
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>легк сер б/к</t>
+          <t>легк б/к сер</t>
         </is>
       </c>
     </row>
@@ -7643,7 +7643,7 @@
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>легк сер б/к</t>
+          <t>легк б/к сер</t>
         </is>
       </c>
     </row>
@@ -7660,7 +7660,7 @@
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>легк сер б/к</t>
+          <t>легк б/к сер</t>
         </is>
       </c>
     </row>
@@ -7677,7 +7677,7 @@
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>легк сер б/к</t>
+          <t>легк б/к сер</t>
         </is>
       </c>
     </row>
@@ -7694,7 +7694,7 @@
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>легк сер б/к</t>
+          <t>легк б/к сер</t>
         </is>
       </c>
     </row>
@@ -7711,7 +7711,7 @@
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>легк сер б/к</t>
+          <t>легк б/к сер</t>
         </is>
       </c>
     </row>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>легк сер б/к</t>
+          <t>легк б/к сер</t>
         </is>
       </c>
     </row>
@@ -7745,7 +7745,7 @@
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>легк сер б/к</t>
+          <t>легк б/к сер</t>
         </is>
       </c>
     </row>
@@ -7762,7 +7762,7 @@
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>легк сер б/к</t>
+          <t>легк б/к сер</t>
         </is>
       </c>
     </row>
@@ -7796,7 +7796,7 @@
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>легк сер б/к</t>
+          <t>легк б/к сер</t>
         </is>
       </c>
     </row>
@@ -7813,7 +7813,7 @@
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>легк сер б/к</t>
+          <t>легк б/к сер</t>
         </is>
       </c>
     </row>
@@ -7830,7 +7830,7 @@
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>легк сер б/к</t>
+          <t>легк б/к сер</t>
         </is>
       </c>
     </row>
@@ -7847,7 +7847,7 @@
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>легк сер б/к</t>
+          <t>легк б/к сер</t>
         </is>
       </c>
     </row>
@@ -7864,7 +7864,7 @@
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>легк сер б/к</t>
+          <t>легк б/к сер</t>
         </is>
       </c>
     </row>
@@ -7881,7 +7881,7 @@
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>легк сер б/к</t>
+          <t>легк б/к сер</t>
         </is>
       </c>
     </row>
@@ -7898,7 +7898,7 @@
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>легк сер б/к</t>
+          <t>легк б/к сер</t>
         </is>
       </c>
     </row>
@@ -7915,7 +7915,7 @@
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>легк сер б/к</t>
+          <t>легк б/к сер</t>
         </is>
       </c>
     </row>
@@ -7932,7 +7932,7 @@
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>легк сер б/к</t>
+          <t>легк б/к сер</t>
         </is>
       </c>
     </row>
@@ -7949,7 +7949,7 @@
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>легк сер б/к</t>
+          <t>легк б/к сер</t>
         </is>
       </c>
     </row>
@@ -7966,7 +7966,7 @@
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>легк сер б/к</t>
+          <t>легк б/к сер</t>
         </is>
       </c>
     </row>
@@ -7983,7 +7983,7 @@
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>легк сер б/к</t>
+          <t>легк б/к сер</t>
         </is>
       </c>
     </row>
@@ -8017,7 +8017,7 @@
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>легк сер б/к</t>
+          <t>легк б/к сер</t>
         </is>
       </c>
     </row>
@@ -8034,7 +8034,7 @@
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>легк сер б/к</t>
+          <t>легк б/к сер</t>
         </is>
       </c>
     </row>
@@ -8051,7 +8051,7 @@
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>легк сер б/к</t>
+          <t>легк б/к сер</t>
         </is>
       </c>
     </row>
@@ -8068,7 +8068,7 @@
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>легк сер б/к</t>
+          <t>легк б/к сер</t>
         </is>
       </c>
     </row>
@@ -8085,7 +8085,7 @@
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>легк сер б/к</t>
+          <t>легк б/к сер</t>
         </is>
       </c>
     </row>
@@ -8102,7 +8102,7 @@
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>легк сер б/к</t>
+          <t>легк б/к сер</t>
         </is>
       </c>
     </row>
@@ -8119,7 +8119,7 @@
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>легк сер б/к</t>
+          <t>легк б/к сер</t>
         </is>
       </c>
     </row>
@@ -8136,7 +8136,7 @@
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>легк сер б/к</t>
+          <t>легк б/к сер</t>
         </is>
       </c>
     </row>
@@ -8153,7 +8153,7 @@
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>легк сер б/к</t>
+          <t>легк б/к сер</t>
         </is>
       </c>
     </row>
@@ -8170,7 +8170,7 @@
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>сер б/к л/г</t>
+          <t>б/к л/г сер</t>
         </is>
       </c>
     </row>
@@ -8187,7 +8187,7 @@
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>сер б/к л/г</t>
+          <t>б/к л/г сер</t>
         </is>
       </c>
     </row>
@@ -8204,7 +8204,7 @@
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>сер б/к л/г</t>
+          <t>б/к л/г сер</t>
         </is>
       </c>
     </row>
@@ -8221,7 +8221,7 @@
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>сер б/к л/г</t>
+          <t>б/к л/г сер</t>
         </is>
       </c>
     </row>
@@ -8306,7 +8306,7 @@
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>сер б/к л/г</t>
+          <t>б/к л/г сер</t>
         </is>
       </c>
     </row>
@@ -8357,7 +8357,7 @@
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>сер б/к</t>
+          <t>б/к сер</t>
         </is>
       </c>
     </row>
@@ -8408,7 +8408,7 @@
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>сер б/к</t>
+          <t>б/к сер</t>
         </is>
       </c>
     </row>
@@ -8425,7 +8425,7 @@
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>сер б/к л/г</t>
+          <t>б/к л/г сер</t>
         </is>
       </c>
     </row>
@@ -8442,7 +8442,7 @@
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>сер л/г</t>
+          <t>л/г сер</t>
         </is>
       </c>
     </row>
@@ -8459,7 +8459,7 @@
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>сер л/г</t>
+          <t>л/г сер</t>
         </is>
       </c>
     </row>
@@ -8476,7 +8476,7 @@
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>легк сер б/к</t>
+          <t>легк б/к сер</t>
         </is>
       </c>
     </row>
@@ -8493,7 +8493,7 @@
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>68 сер груз</t>
+          <t>68 груз сер</t>
         </is>
       </c>
     </row>
@@ -8510,7 +8510,7 @@
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>68 сер груз</t>
+          <t>68 груз сер</t>
         </is>
       </c>
     </row>
@@ -8527,7 +8527,7 @@
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>58 сер груз</t>
+          <t>58 груз сер</t>
         </is>
       </c>
     </row>
@@ -8544,7 +8544,7 @@
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>58 сер груз</t>
+          <t>58 груз сер</t>
         </is>
       </c>
     </row>
@@ -8561,7 +8561,7 @@
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>54 сер груз</t>
+          <t>54 груз сер</t>
         </is>
       </c>
     </row>
@@ -8578,7 +8578,7 @@
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>48 сер груз</t>
+          <t>48 груз сер</t>
         </is>
       </c>
     </row>
@@ -8595,7 +8595,7 @@
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>48 сер груз</t>
+          <t>48 груз сер</t>
         </is>
       </c>
     </row>
@@ -8612,7 +8612,7 @@
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>Type LS-2 сер груз</t>
+          <t>груз Type LS-2 сер</t>
         </is>
       </c>
     </row>
@@ -8629,7 +8629,7 @@
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>Type сер H груз</t>
+          <t>груз Type сер H</t>
         </is>
       </c>
     </row>
@@ -8646,7 +8646,7 @@
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>Type сер C груз</t>
+          <t>груз Type сер C</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>Type LS-2 сер груз</t>
+          <t>груз Type LS-2 сер</t>
         </is>
       </c>
     </row>
@@ -8731,7 +8731,7 @@
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>Type сер H груз</t>
+          <t>груз Type сер H</t>
         </is>
       </c>
     </row>
@@ -8748,7 +8748,7 @@
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>Type сер C груз</t>
+          <t>груз Type сер C</t>
         </is>
       </c>
     </row>
@@ -8867,7 +8867,7 @@
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>сер груз</t>
+          <t>груз сер</t>
         </is>
       </c>
     </row>
@@ -8884,7 +8884,7 @@
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>сер б/к груз</t>
+          <t>груз б/к сер</t>
         </is>
       </c>
     </row>
@@ -8901,7 +8901,7 @@
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>сер груз</t>
+          <t>груз сер</t>
         </is>
       </c>
     </row>
@@ -8918,7 +8918,7 @@
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>сер груз</t>
+          <t>груз сер</t>
         </is>
       </c>
     </row>
@@ -8935,7 +8935,7 @@
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>сер груз</t>
+          <t>груз сер</t>
         </is>
       </c>
     </row>
@@ -8952,7 +8952,7 @@
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>173G сер б/к груз</t>
+          <t>173G груз б/к сер</t>
         </is>
       </c>
     </row>
@@ -8969,7 +8969,7 @@
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>173G сер груз</t>
+          <t>173G груз сер</t>
         </is>
       </c>
     </row>
@@ -8986,7 +8986,7 @@
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>173G сер груз</t>
+          <t>173G груз сер</t>
         </is>
       </c>
     </row>
@@ -9003,7 +9003,7 @@
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>173G сер груз</t>
+          <t>173G груз сер</t>
         </is>
       </c>
     </row>
@@ -9020,7 +9020,7 @@
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>173G сер груз</t>
+          <t>173G груз сер</t>
         </is>
       </c>
     </row>
@@ -9037,7 +9037,7 @@
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>173G сер груз</t>
+          <t>173G груз сер</t>
         </is>
       </c>
     </row>
@@ -9071,7 +9071,7 @@
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>168J сер груз</t>
+          <t>168J груз сер</t>
         </is>
       </c>
     </row>
@@ -9088,7 +9088,7 @@
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>сер б/к груз</t>
+          <t>груз б/к сер</t>
         </is>
       </c>
     </row>

--- a/src/Tyres.xlsx
+++ b/src/Tyres.xlsx
@@ -524,7 +524,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>28 б/к сер</t>
+          <t>28 сер б/к</t>
         </is>
       </c>
     </row>
@@ -558,7 +558,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>32 б/к сер</t>
+          <t>32 сер б/к</t>
         </is>
       </c>
     </row>
@@ -592,7 +592,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>28 груз б/к сер</t>
+          <t>28 груз сер б/к</t>
         </is>
       </c>
     </row>
@@ -626,7 +626,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>32 груз б/к сер</t>
+          <t>32 груз сер б/к</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>28 груз б/к сер</t>
+          <t>28 груз сер б/к</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>32 груз б/к сер</t>
+          <t>32 груз сер б/к</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>груз Type LS-2 сер</t>
+          <t>LS-2 Type груз сер</t>
         </is>
       </c>
     </row>
@@ -728,7 +728,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>груз Type сер H</t>
+          <t>Type груз H сер</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>груз Type сер C</t>
+          <t>C Type груз сер</t>
         </is>
       </c>
     </row>
@@ -762,7 +762,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>груз Type LS-2 сер</t>
+          <t>LS-2 Type груз сер</t>
         </is>
       </c>
     </row>
@@ -779,7 +779,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>груз Type сер H</t>
+          <t>Type груз H сер</t>
         </is>
       </c>
     </row>
@@ -796,7 +796,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>груз Type сер C</t>
+          <t>C Type груз сер</t>
         </is>
       </c>
     </row>
@@ -813,7 +813,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>193B груз Type LS-2 сер</t>
+          <t>193B LS-2 Type груз сер</t>
         </is>
       </c>
     </row>
@@ -830,7 +830,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>193B груз Type сер H</t>
+          <t>193B Type груз H сер</t>
         </is>
       </c>
     </row>
@@ -847,7 +847,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>193B груз Type сер C</t>
+          <t>193B C Type груз сер</t>
         </is>
       </c>
     </row>
@@ -915,7 +915,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>20 груз б/к сер</t>
+          <t>20 груз сер б/к</t>
         </is>
       </c>
     </row>
@@ -966,7 +966,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>24 груз б/к сер</t>
+          <t>24 груз сер б/к</t>
         </is>
       </c>
     </row>
@@ -983,7 +983,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>28 груз б/к сер</t>
+          <t>28 груз сер б/к</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>20 груз б/к сер</t>
+          <t>20 груз сер б/к</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>16 б/к сер</t>
+          <t>16 сер б/к</t>
         </is>
       </c>
     </row>
@@ -1170,7 +1170,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>28 б/к сер</t>
+          <t>28 сер б/к</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>177 186A2 Type LS-2 сер</t>
+          <t>177 186A2 LS-2 Type сер</t>
         </is>
       </c>
     </row>
@@ -1255,7 +1255,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>груз Type LS-2 сер</t>
+          <t>LS-2 Type груз сер</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>177 186A2 Type сер H</t>
+          <t>177 186A2 Type H сер</t>
         </is>
       </c>
     </row>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>груз Type сер H</t>
+          <t>Type груз H сер</t>
         </is>
       </c>
     </row>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>177 186A2 Type сер C</t>
+          <t>177 186A2 C Type сер</t>
         </is>
       </c>
     </row>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>груз Type сер C</t>
+          <t>C Type груз сер</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>32 груз б/к сер</t>
+          <t>32 груз сер б/к</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>36 груз б/к сер</t>
+          <t>36 груз сер б/к</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1442,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>28 б/к сер</t>
+          <t>28 сер б/к</t>
         </is>
       </c>
     </row>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>185B Type б/к LS-2</t>
+          <t>185B LS-2 Type б/к</t>
         </is>
       </c>
     </row>
@@ -1527,7 +1527,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>груз Type LS-2 сер</t>
+          <t>LS-2 Type груз сер</t>
         </is>
       </c>
     </row>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>185B Type б/к H</t>
+          <t>185B Type H б/к</t>
         </is>
       </c>
     </row>
@@ -1561,7 +1561,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>груз Type сер H</t>
+          <t>Type груз H сер</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>185B Type б/к C</t>
+          <t>185B C Type б/к</t>
         </is>
       </c>
     </row>
@@ -1595,7 +1595,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>груз Type сер C</t>
+          <t>C Type груз сер</t>
         </is>
       </c>
     </row>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>170B LS-2 сер L-2</t>
+          <t>170B LS-2 L-2 сер</t>
         </is>
       </c>
     </row>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>170B сер H L-2</t>
+          <t>170B L-2 H сер</t>
         </is>
       </c>
     </row>
@@ -1663,7 +1663,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>170B сер L-2 C</t>
+          <t>170B L-2 C сер</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>12 груз б/к сер</t>
+          <t>12 груз сер б/к</t>
         </is>
       </c>
     </row>
@@ -1782,7 +1782,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>16 груз б/к сер</t>
+          <t>16 груз сер б/к</t>
         </is>
       </c>
     </row>
@@ -1816,7 +1816,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>20 б/к сер</t>
+          <t>20 сер б/к</t>
         </is>
       </c>
     </row>
@@ -1850,7 +1850,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>182A2 груз LS-2 сер</t>
+          <t>182A2 LS-2 груз сер</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>182A2 груз сер H</t>
+          <t>182A2 груз H сер</t>
         </is>
       </c>
     </row>
@@ -1884,7 +1884,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>182A2 груз сер C</t>
+          <t>182A2 C груз сер</t>
         </is>
       </c>
     </row>
@@ -1901,7 +1901,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>182A2 груз б/к LS-2 сер</t>
+          <t>182A2 LS-2 груз сер б/к</t>
         </is>
       </c>
     </row>
@@ -1918,7 +1918,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>182A2 груз б/к сер H</t>
+          <t>182A2 груз H сер б/к</t>
         </is>
       </c>
     </row>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>182A2 груз б/к сер C</t>
+          <t>182A2 C груз сер б/к</t>
         </is>
       </c>
     </row>
@@ -1952,7 +1952,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>груз б/к сер</t>
+          <t>груз сер б/к</t>
         </is>
       </c>
     </row>
@@ -1969,7 +1969,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>182A2 груз б/к LS-2 сер</t>
+          <t>182A2 LS-2 груз сер б/к</t>
         </is>
       </c>
     </row>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>182A2 груз б/к сер H</t>
+          <t>182A2 груз H сер б/к</t>
         </is>
       </c>
     </row>
@@ -2003,7 +2003,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>182A2 груз б/к сер C</t>
+          <t>182A2 C груз сер б/к</t>
         </is>
       </c>
     </row>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>182A2 груз LS-2 сер</t>
+          <t>182A2 LS-2 груз сер</t>
         </is>
       </c>
     </row>
@@ -2054,7 +2054,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>182A2 груз сер H</t>
+          <t>182A2 груз H сер</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>182A2 груз сер C</t>
+          <t>182A2 C груз сер</t>
         </is>
       </c>
     </row>
@@ -2292,7 +2292,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>26 б/к сер</t>
+          <t>26 сер б/к</t>
         </is>
       </c>
     </row>
@@ -2411,7 +2411,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>груз Type LS-2 сер</t>
+          <t>LS-2 Type груз сер</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>груз Type сер H</t>
+          <t>Type груз H сер</t>
         </is>
       </c>
     </row>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>груз Type сер C</t>
+          <t>C Type груз сер</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>200B груз Type LS-2 сер</t>
+          <t>200B LS-2 Type груз сер</t>
         </is>
       </c>
     </row>
@@ -2479,7 +2479,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>200B груз Type сер H</t>
+          <t>200B Type груз H сер</t>
         </is>
       </c>
     </row>
@@ -2496,7 +2496,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>200B груз Type сер C</t>
+          <t>200B C Type груз сер</t>
         </is>
       </c>
     </row>
@@ -2513,7 +2513,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>200B груз Type LS-2 сер</t>
+          <t>200B LS-2 Type груз сер</t>
         </is>
       </c>
     </row>
@@ -2530,7 +2530,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>200B груз Type сер H</t>
+          <t>200B Type груз H сер</t>
         </is>
       </c>
     </row>
@@ -2547,7 +2547,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>200B груз Type сер C</t>
+          <t>200B C Type груз сер</t>
         </is>
       </c>
     </row>
@@ -2564,7 +2564,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>185B Type б/к LS-2</t>
+          <t>185B LS-2 Type б/к</t>
         </is>
       </c>
     </row>
@@ -2581,7 +2581,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>185B груз Type LS-2 сер</t>
+          <t>185B LS-2 Type груз сер</t>
         </is>
       </c>
     </row>
@@ -2598,7 +2598,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>185B Type б/к H</t>
+          <t>185B Type H б/к</t>
         </is>
       </c>
     </row>
@@ -2615,7 +2615,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>185B груз Type сер H</t>
+          <t>185B Type груз H сер</t>
         </is>
       </c>
     </row>
@@ -2632,7 +2632,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>185B Type б/к C</t>
+          <t>185B C Type б/к</t>
         </is>
       </c>
     </row>
@@ -2649,7 +2649,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>185B груз Type сер C</t>
+          <t>185B C Type груз сер</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>185B груз Type LS-2 сер</t>
+          <t>185B LS-2 Type груз сер</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>185B груз Type сер H</t>
+          <t>185B Type груз H сер</t>
         </is>
       </c>
     </row>
@@ -2700,7 +2700,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>185B груз Type сер C</t>
+          <t>185B C Type груз сер</t>
         </is>
       </c>
     </row>
@@ -2717,7 +2717,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>груз Type LS-2 сер</t>
+          <t>LS-2 Type груз сер</t>
         </is>
       </c>
     </row>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>груз Type сер H</t>
+          <t>Type груз H сер</t>
         </is>
       </c>
     </row>
@@ -2751,7 +2751,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>груз Type сер C</t>
+          <t>C Type груз сер</t>
         </is>
       </c>
     </row>
@@ -2768,7 +2768,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>груз Type LS-2 сер</t>
+          <t>LS-2 Type груз сер</t>
         </is>
       </c>
     </row>
@@ -2785,7 +2785,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>груз Type сер H</t>
+          <t>Type груз H сер</t>
         </is>
       </c>
     </row>
@@ -2802,7 +2802,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>груз Type сер C</t>
+          <t>C Type груз сер</t>
         </is>
       </c>
     </row>
@@ -2917,7 +2917,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>165A8 б/к сх сер</t>
+          <t>165A8 сх сер б/к</t>
         </is>
       </c>
     </row>
@@ -3070,7 +3070,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>12 б/к сер</t>
+          <t>12 сер б/к</t>
         </is>
       </c>
     </row>
@@ -3104,7 +3104,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>16 б/к сер</t>
+          <t>16 сер б/к</t>
         </is>
       </c>
     </row>
@@ -3274,7 +3274,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>158D б/к сер</t>
+          <t>158D сер б/к</t>
         </is>
       </c>
     </row>
@@ -3427,7 +3427,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>12 б/к сер</t>
+          <t>12 сер б/к</t>
         </is>
       </c>
     </row>
@@ -3546,7 +3546,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>141A8 б/к сх сер</t>
+          <t>141A8 сх сер б/к</t>
         </is>
       </c>
     </row>
@@ -3648,7 +3648,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>б/к сх сер</t>
+          <t>сх сер б/к</t>
         </is>
       </c>
     </row>
@@ -3886,7 +3886,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>114A8 б/к сер</t>
+          <t>114A8 сер б/к</t>
         </is>
       </c>
     </row>
@@ -3937,7 +3937,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>148A8 б/к сер</t>
+          <t>148A8 сер б/к</t>
         </is>
       </c>
     </row>
@@ -4583,7 +4583,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>сх сер L-2</t>
+          <t>L-2 сх сер</t>
         </is>
       </c>
     </row>
@@ -4617,7 +4617,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>сх сер L-2</t>
+          <t>L-2 сх сер</t>
         </is>
       </c>
     </row>
@@ -4804,7 +4804,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>167A8 б/к сер</t>
+          <t>167A8 сер б/к</t>
         </is>
       </c>
     </row>
@@ -4855,7 +4855,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>178A8 б/к сер</t>
+          <t>178A8 сер б/к</t>
         </is>
       </c>
     </row>
@@ -5008,7 +5008,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>168A8 б/к сер</t>
+          <t>168A8 сер б/к</t>
         </is>
       </c>
     </row>
@@ -5161,7 +5161,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>150A8 б/к сер</t>
+          <t>150A8 сер б/к</t>
         </is>
       </c>
     </row>
@@ -5433,7 +5433,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>груз камневыт сер</t>
+          <t>камневыт груз сер</t>
         </is>
       </c>
     </row>
@@ -6045,7 +6045,7 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>груз камневыт сер</t>
+          <t>камневыт груз сер</t>
         </is>
       </c>
     </row>
@@ -6147,7 +6147,7 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>груз б/к сер</t>
+          <t>груз сер б/к</t>
         </is>
       </c>
     </row>
@@ -6249,7 +6249,7 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>груз б/к сер</t>
+          <t>груз сер б/к</t>
         </is>
       </c>
     </row>
@@ -6283,7 +6283,7 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>груз б/к сер</t>
+          <t>груз сер б/к</t>
         </is>
       </c>
     </row>
@@ -6436,7 +6436,7 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>легк б/к сер</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -6453,7 +6453,7 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>легк б/к сер</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -6470,7 +6470,7 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>легк б/к сер</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -6487,7 +6487,7 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>легк б/к сер</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -6521,7 +6521,7 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>легк б/к сер</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -6538,7 +6538,7 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>легк б/к сер</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -6572,7 +6572,7 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>легк б/к сер</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -6606,7 +6606,7 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>легк б/к сер</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -6623,7 +6623,7 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>легк б/к сер</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -6640,7 +6640,7 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>легк б/к сер</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -6674,7 +6674,7 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>легк б/к сер</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -6691,7 +6691,7 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>легк б/к сер</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -6708,7 +6708,7 @@
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>легк б/к сер</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>легк б/к сер</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -6742,7 +6742,7 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>легк б/к сер</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -6759,7 +6759,7 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>легк б/к сер</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -6793,7 +6793,7 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>б/к сер</t>
+          <t>сер б/к</t>
         </is>
       </c>
     </row>
@@ -6810,7 +6810,7 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>легк б/к сер</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -6844,7 +6844,7 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>легк б/к сер</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -6878,7 +6878,7 @@
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>легк б/к сер</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -6912,7 +6912,7 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>легк б/к сер</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -6946,7 +6946,7 @@
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>легк б/к сер</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -6963,7 +6963,7 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>легк б/к сер</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>легк б/к сер</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -7014,7 +7014,7 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>легк б/к сер</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -7031,7 +7031,7 @@
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>легк б/к сер</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -7065,7 +7065,7 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>легк б/к сер</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -7082,7 +7082,7 @@
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>легк б/к сер</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -7099,7 +7099,7 @@
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>легк б/к сер</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -7116,7 +7116,7 @@
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>легк б/к сер</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -7150,7 +7150,7 @@
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>легк б/к сер</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -7167,7 +7167,7 @@
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>легк б/к сер</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>легк б/к сер</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -7201,7 +7201,7 @@
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>легк б/к сер</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -7235,7 +7235,7 @@
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>легк б/к сер</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -7252,7 +7252,7 @@
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>легк б/к сер</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -7286,7 +7286,7 @@
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>легк б/к сер</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -7303,7 +7303,7 @@
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>легк б/к сер</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -7320,7 +7320,7 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>легк б/к сер</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -7354,7 +7354,7 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>легк б/к сер</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -7371,7 +7371,7 @@
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>легк б/к сер</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -7388,7 +7388,7 @@
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>легк б/к сер</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -7405,7 +7405,7 @@
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>легк б/к сер</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -7422,7 +7422,7 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>легк б/к сер</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -7439,7 +7439,7 @@
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>легк б/к сер</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -7456,7 +7456,7 @@
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>легк б/к сер</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -7473,7 +7473,7 @@
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>легк б/к сер</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -7490,7 +7490,7 @@
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>легк б/к сер</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -7507,7 +7507,7 @@
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>легк б/к сер</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -7524,7 +7524,7 @@
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>легк б/к сер</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -7541,7 +7541,7 @@
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>легк б/к сер</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -7558,7 +7558,7 @@
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>легк б/к сер</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -7575,7 +7575,7 @@
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>легк б/к сер</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -7592,7 +7592,7 @@
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>легк б/к сер</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -7626,7 +7626,7 @@
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>легк б/к сер</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -7643,7 +7643,7 @@
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>легк б/к сер</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -7660,7 +7660,7 @@
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>легк б/к сер</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -7677,7 +7677,7 @@
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>легк б/к сер</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -7694,7 +7694,7 @@
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>легк б/к сер</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -7711,7 +7711,7 @@
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>легк б/к сер</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>легк б/к сер</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -7745,7 +7745,7 @@
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>легк б/к сер</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -7762,7 +7762,7 @@
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>легк б/к сер</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -7796,7 +7796,7 @@
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>легк б/к сер</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -7813,7 +7813,7 @@
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>легк б/к сер</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -7830,7 +7830,7 @@
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>легк б/к сер</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -7847,7 +7847,7 @@
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>легк б/к сер</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -7864,7 +7864,7 @@
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>легк б/к сер</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -7881,7 +7881,7 @@
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>легк б/к сер</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -7898,7 +7898,7 @@
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>легк б/к сер</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -7915,7 +7915,7 @@
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>легк б/к сер</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -7932,7 +7932,7 @@
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>легк б/к сер</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -7949,7 +7949,7 @@
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>легк б/к сер</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -7966,7 +7966,7 @@
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>легк б/к сер</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -7983,7 +7983,7 @@
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>легк б/к сер</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -8017,7 +8017,7 @@
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>легк б/к сер</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -8034,7 +8034,7 @@
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>легк б/к сер</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -8051,7 +8051,7 @@
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>легк б/к сер</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -8068,7 +8068,7 @@
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>легк б/к сер</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -8085,7 +8085,7 @@
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>легк б/к сер</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -8102,7 +8102,7 @@
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>легк б/к сер</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -8119,7 +8119,7 @@
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>легк б/к сер</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -8136,7 +8136,7 @@
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>легк б/к сер</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -8153,7 +8153,7 @@
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>легк б/к сер</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -8170,7 +8170,7 @@
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>б/к л/г сер</t>
+          <t>л/г сер б/к</t>
         </is>
       </c>
     </row>
@@ -8187,7 +8187,7 @@
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>б/к л/г сер</t>
+          <t>л/г сер б/к</t>
         </is>
       </c>
     </row>
@@ -8204,7 +8204,7 @@
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>б/к л/г сер</t>
+          <t>л/г сер б/к</t>
         </is>
       </c>
     </row>
@@ -8221,7 +8221,7 @@
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>б/к л/г сер</t>
+          <t>л/г сер б/к</t>
         </is>
       </c>
     </row>
@@ -8306,7 +8306,7 @@
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>б/к л/г сер</t>
+          <t>л/г сер б/к</t>
         </is>
       </c>
     </row>
@@ -8357,7 +8357,7 @@
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>б/к сер</t>
+          <t>сер б/к</t>
         </is>
       </c>
     </row>
@@ -8408,7 +8408,7 @@
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>б/к сер</t>
+          <t>сер б/к</t>
         </is>
       </c>
     </row>
@@ -8425,7 +8425,7 @@
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>б/к л/г сер</t>
+          <t>л/г сер б/к</t>
         </is>
       </c>
     </row>
@@ -8476,7 +8476,7 @@
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>легк б/к сер</t>
+          <t>легк сер б/к</t>
         </is>
       </c>
     </row>
@@ -8612,7 +8612,7 @@
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>груз Type LS-2 сер</t>
+          <t>LS-2 Type груз сер</t>
         </is>
       </c>
     </row>
@@ -8629,7 +8629,7 @@
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>груз Type сер H</t>
+          <t>Type груз H сер</t>
         </is>
       </c>
     </row>
@@ -8646,7 +8646,7 @@
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>груз Type сер C</t>
+          <t>C Type груз сер</t>
         </is>
       </c>
     </row>
@@ -8663,7 +8663,7 @@
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>210B Type LS-2 сер</t>
+          <t>210B LS-2 Type сер</t>
         </is>
       </c>
     </row>
@@ -8680,7 +8680,7 @@
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>210B Type сер H</t>
+          <t>210B Type H сер</t>
         </is>
       </c>
     </row>
@@ -8697,7 +8697,7 @@
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>210B Type сер C</t>
+          <t>210B C Type сер</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>груз Type LS-2 сер</t>
+          <t>LS-2 Type груз сер</t>
         </is>
       </c>
     </row>
@@ -8731,7 +8731,7 @@
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>груз Type сер H</t>
+          <t>Type груз H сер</t>
         </is>
       </c>
     </row>
@@ -8748,7 +8748,7 @@
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>груз Type сер C</t>
+          <t>C Type груз сер</t>
         </is>
       </c>
     </row>
@@ -8765,7 +8765,7 @@
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>202B Type LS-2 сер</t>
+          <t>202B LS-2 Type сер</t>
         </is>
       </c>
     </row>
@@ -8782,7 +8782,7 @@
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>202B Type сер H</t>
+          <t>202B Type H сер</t>
         </is>
       </c>
     </row>
@@ -8799,7 +8799,7 @@
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>202B Type сер C</t>
+          <t>202B C Type сер</t>
         </is>
       </c>
     </row>
@@ -8816,7 +8816,7 @@
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>202B Type LS-2 сер</t>
+          <t>202B LS-2 Type сер</t>
         </is>
       </c>
     </row>
@@ -8833,7 +8833,7 @@
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>202B Type сер H</t>
+          <t>202B Type H сер</t>
         </is>
       </c>
     </row>
@@ -8850,7 +8850,7 @@
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>202B Type сер C</t>
+          <t>202B C Type сер</t>
         </is>
       </c>
     </row>
@@ -8884,7 +8884,7 @@
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>груз б/к сер</t>
+          <t>груз сер б/к</t>
         </is>
       </c>
     </row>
@@ -8952,7 +8952,7 @@
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>173G груз б/к сер</t>
+          <t>173G груз сер б/к</t>
         </is>
       </c>
     </row>
@@ -9088,7 +9088,7 @@
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>груз б/к сер</t>
+          <t>груз сер б/к</t>
         </is>
       </c>
     </row>
